--- a/data/raw/annex_c.xlsx
+++ b/data/raw/annex_c.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAALV\Documents\prode-mundial-2026\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAALV\Documents\portfolio-review\prode-mundial-2026\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4960443-9628-4A8C-8F2C-D90E3219F381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2421F996-266F-4B6D-8465-05C7A05EA53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C25317B4-E939-484A-8B4F-30B1064F8F3E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4465" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4465" uniqueCount="517">
   <si>
     <t>1A</t>
   </si>
@@ -107,1119 +107,132 @@
     <t>EFGHIJKL</t>
   </si>
   <si>
-    <t>DFGHIJ</t>
-  </si>
-  <si>
-    <t>DEGHIJ</t>
-  </si>
-  <si>
-    <t>DEFHIJ</t>
-  </si>
-  <si>
-    <t>DEFGIJ</t>
-  </si>
-  <si>
-    <t>DEFGHJ</t>
-  </si>
-  <si>
-    <t>DEFGHI</t>
-  </si>
-  <si>
-    <t>DEFGHIJ</t>
-  </si>
-  <si>
-    <t>CFGHIJ</t>
-  </si>
-  <si>
-    <t>CEGHIJ</t>
-  </si>
-  <si>
-    <t>CEFHIJ</t>
-  </si>
-  <si>
-    <t>CEFGIJ</t>
-  </si>
-  <si>
-    <t>CEFGHJ</t>
-  </si>
-  <si>
-    <t>CEFGHI</t>
-  </si>
-  <si>
-    <t>CEFGHIJ</t>
-  </si>
-  <si>
-    <t>CDGHIJ</t>
-  </si>
-  <si>
-    <t>CDFHIJ</t>
-  </si>
-  <si>
-    <t>CDFGIJ</t>
-  </si>
-  <si>
-    <t>CDFGHJ</t>
-  </si>
-  <si>
-    <t>CDFGHI</t>
-  </si>
-  <si>
-    <t>CDFGHIJ</t>
-  </si>
-  <si>
-    <t>CDEHIJ</t>
-  </si>
-  <si>
-    <t>CDEGIJ</t>
-  </si>
-  <si>
-    <t>CDEGHJ</t>
-  </si>
-  <si>
-    <t>CDEGHI</t>
-  </si>
-  <si>
-    <t>CDEGHIJ</t>
-  </si>
-  <si>
-    <t>CDEFIJ</t>
-  </si>
-  <si>
-    <t>CDEFHJ</t>
-  </si>
-  <si>
-    <t>CDEFHI</t>
-  </si>
-  <si>
-    <t>CDEFHIJ</t>
-  </si>
-  <si>
-    <t>CDEFGJ</t>
-  </si>
-  <si>
-    <t>CDEFGI</t>
-  </si>
-  <si>
-    <t>CDEFGIJ</t>
-  </si>
-  <si>
-    <t>CDEFGH</t>
-  </si>
-  <si>
-    <t>CDEFGHJ</t>
-  </si>
-  <si>
-    <t>CDEFGHI</t>
-  </si>
-  <si>
     <t>CDEFGHIJ</t>
   </si>
   <si>
-    <t>BFGHIJ</t>
-  </si>
-  <si>
-    <t>BEGHIJ</t>
-  </si>
-  <si>
-    <t>BEFHIJ</t>
-  </si>
-  <si>
-    <t>BEFGIJ</t>
-  </si>
-  <si>
-    <t>BEFGHJ</t>
-  </si>
-  <si>
-    <t>BEFGHI</t>
-  </si>
-  <si>
-    <t>BEFGHIJ</t>
-  </si>
-  <si>
-    <t>BDGHIJ</t>
-  </si>
-  <si>
-    <t>BDFHIJ</t>
-  </si>
-  <si>
-    <t>BDFGIJ</t>
-  </si>
-  <si>
-    <t>BDFGHJ</t>
-  </si>
-  <si>
-    <t>BDFGHI</t>
-  </si>
-  <si>
-    <t>BDFGHIJ</t>
-  </si>
-  <si>
-    <t>BDEHIJ</t>
-  </si>
-  <si>
-    <t>BDEGIJ</t>
-  </si>
-  <si>
-    <t>BDEGHJ</t>
-  </si>
-  <si>
-    <t>BDEGHI</t>
-  </si>
-  <si>
-    <t>BDEGHIJ</t>
-  </si>
-  <si>
-    <t>BDEFIJ</t>
-  </si>
-  <si>
-    <t>BDEFHJ</t>
-  </si>
-  <si>
-    <t>BDEFHI</t>
-  </si>
-  <si>
-    <t>BDEFHIJ</t>
-  </si>
-  <si>
-    <t>BDEFGJ</t>
-  </si>
-  <si>
-    <t>BDEFGI</t>
-  </si>
-  <si>
-    <t>BDEFGIJ</t>
-  </si>
-  <si>
-    <t>BDEFGH</t>
-  </si>
-  <si>
-    <t>BDEFGHJ</t>
-  </si>
-  <si>
-    <t>BDEFGHI</t>
-  </si>
-  <si>
     <t>BDEFGHIJ</t>
   </si>
   <si>
-    <t>BCGHIJ</t>
-  </si>
-  <si>
-    <t>BCFHIJ</t>
-  </si>
-  <si>
-    <t>BCFGIJ</t>
-  </si>
-  <si>
-    <t>BCFGHJ</t>
-  </si>
-  <si>
-    <t>BCFGHI</t>
-  </si>
-  <si>
-    <t>BCFGHIJ</t>
-  </si>
-  <si>
-    <t>BCEHIJ</t>
-  </si>
-  <si>
-    <t>BCEGIJ</t>
-  </si>
-  <si>
-    <t>BCEGHJ</t>
-  </si>
-  <si>
-    <t>BCEGHI</t>
-  </si>
-  <si>
-    <t>BCEGHIJ</t>
-  </si>
-  <si>
-    <t>BCEFIJ</t>
-  </si>
-  <si>
-    <t>BCEFHJ</t>
-  </si>
-  <si>
-    <t>BCEFHI</t>
-  </si>
-  <si>
-    <t>BCEFHIJ</t>
-  </si>
-  <si>
-    <t>BCEFGJ</t>
-  </si>
-  <si>
-    <t>BCEFGI</t>
-  </si>
-  <si>
-    <t>BCEFGIJ</t>
-  </si>
-  <si>
-    <t>BCEFGH</t>
-  </si>
-  <si>
-    <t>BCEFGHJ</t>
-  </si>
-  <si>
-    <t>BCEFGHI</t>
-  </si>
-  <si>
     <t>BCEFGHIJ</t>
   </si>
   <si>
-    <t>BCDHIJ</t>
-  </si>
-  <si>
-    <t>BCDGIJ</t>
-  </si>
-  <si>
-    <t>BCDGHJ</t>
-  </si>
-  <si>
-    <t>BCDGHI</t>
-  </si>
-  <si>
-    <t>BCDGHIJ</t>
-  </si>
-  <si>
-    <t>BCDFIJ</t>
-  </si>
-  <si>
-    <t>BCDFHJ</t>
-  </si>
-  <si>
-    <t>BCDFHI</t>
-  </si>
-  <si>
-    <t>BCDFHIJ</t>
-  </si>
-  <si>
-    <t>BCDFGJ</t>
-  </si>
-  <si>
-    <t>BCDFGI</t>
-  </si>
-  <si>
-    <t>BCDFGIJ</t>
-  </si>
-  <si>
-    <t>BCDFGH</t>
-  </si>
-  <si>
-    <t>BCDFGHJ</t>
-  </si>
-  <si>
-    <t>BCDFGHI</t>
-  </si>
-  <si>
     <t>BCDFGHIJ</t>
   </si>
   <si>
-    <t>BCDEIJ</t>
-  </si>
-  <si>
-    <t>BCDEHJ</t>
-  </si>
-  <si>
-    <t>BCDEHI</t>
-  </si>
-  <si>
-    <t>BCDEHIJ</t>
-  </si>
-  <si>
-    <t>BCDEGJ</t>
-  </si>
-  <si>
-    <t>BCDEGI</t>
-  </si>
-  <si>
-    <t>BCDEGIJ</t>
-  </si>
-  <si>
-    <t>BCDEGH</t>
-  </si>
-  <si>
-    <t>BCDEGHJ</t>
-  </si>
-  <si>
-    <t>BCDEGHI</t>
-  </si>
-  <si>
     <t>BCDEGHIJ</t>
   </si>
   <si>
-    <t>BCDEFJ</t>
-  </si>
-  <si>
-    <t>BCDEFI</t>
-  </si>
-  <si>
-    <t>BCDEFIJ</t>
-  </si>
-  <si>
-    <t>BCDEFH</t>
-  </si>
-  <si>
-    <t>BCDEFHJ</t>
-  </si>
-  <si>
-    <t>BCDEFHI</t>
-  </si>
-  <si>
     <t>BCDEFHIJ</t>
   </si>
   <si>
-    <t>BCDEFG</t>
-  </si>
-  <si>
-    <t>BCDEFGJ</t>
-  </si>
-  <si>
-    <t>BCDEFGI</t>
-  </si>
-  <si>
     <t>BCDEFGIJ</t>
   </si>
   <si>
-    <t>BCDEFGH</t>
-  </si>
-  <si>
     <t>BCDEFGHJ</t>
   </si>
   <si>
     <t>BCDEFGHI</t>
   </si>
   <si>
-    <t>AFGHIJ</t>
-  </si>
-  <si>
-    <t>AEGHIJ</t>
-  </si>
-  <si>
-    <t>AEFHIJ</t>
-  </si>
-  <si>
-    <t>AEFGIJ</t>
-  </si>
-  <si>
-    <t>AEFGHJ</t>
-  </si>
-  <si>
-    <t>AEFGHI</t>
-  </si>
-  <si>
-    <t>AEFGHIJ</t>
-  </si>
-  <si>
-    <t>ADGHIJ</t>
-  </si>
-  <si>
-    <t>ADFHIJ</t>
-  </si>
-  <si>
-    <t>ADFGIJ</t>
-  </si>
-  <si>
-    <t>ADFGHJ</t>
-  </si>
-  <si>
-    <t>ADFGHI</t>
-  </si>
-  <si>
-    <t>ADFGHIJ</t>
-  </si>
-  <si>
-    <t>ADEHIJ</t>
-  </si>
-  <si>
-    <t>ADEGIJ</t>
-  </si>
-  <si>
-    <t>ADEGHJ</t>
-  </si>
-  <si>
-    <t>ADEGHI</t>
-  </si>
-  <si>
-    <t>ADEGHIJ</t>
-  </si>
-  <si>
-    <t>ADEFIJ</t>
-  </si>
-  <si>
-    <t>ADEFHJ</t>
-  </si>
-  <si>
-    <t>ADEFHI</t>
-  </si>
-  <si>
-    <t>ADEFHIJ</t>
-  </si>
-  <si>
-    <t>ADEFGJ</t>
-  </si>
-  <si>
-    <t>ADEFGI</t>
-  </si>
-  <si>
-    <t>ADEFGIJ</t>
-  </si>
-  <si>
-    <t>ADEFGH</t>
-  </si>
-  <si>
-    <t>ADEFGHJ</t>
-  </si>
-  <si>
-    <t>ADEFGHI</t>
-  </si>
-  <si>
     <t>ADEFGHIJ</t>
   </si>
   <si>
-    <t>ACGHIJ</t>
-  </si>
-  <si>
-    <t>ACFHIJ</t>
-  </si>
-  <si>
-    <t>ACFGIJ</t>
-  </si>
-  <si>
-    <t>ACFGHJ</t>
-  </si>
-  <si>
-    <t>ACFGHI</t>
-  </si>
-  <si>
-    <t>ACFGHIJ</t>
-  </si>
-  <si>
-    <t>ACEHIJ</t>
-  </si>
-  <si>
-    <t>ACEGIJ</t>
-  </si>
-  <si>
-    <t>ACEGHJ</t>
-  </si>
-  <si>
-    <t>ACEGHI</t>
-  </si>
-  <si>
-    <t>ACEGHIJ</t>
-  </si>
-  <si>
-    <t>ACEFIJ</t>
-  </si>
-  <si>
-    <t>ACEFHJ</t>
-  </si>
-  <si>
-    <t>ACEFHI</t>
-  </si>
-  <si>
-    <t>ACEFHIJ</t>
-  </si>
-  <si>
-    <t>ACEFGJ</t>
-  </si>
-  <si>
-    <t>ACEFGI</t>
-  </si>
-  <si>
-    <t>ACEFGIJ</t>
-  </si>
-  <si>
-    <t>ACEFGH</t>
-  </si>
-  <si>
-    <t>ACEFGHJ</t>
-  </si>
-  <si>
-    <t>ACEFGHI</t>
-  </si>
-  <si>
     <t>ACEFGHIJ</t>
   </si>
   <si>
-    <t>ACDHIJ</t>
-  </si>
-  <si>
-    <t>ACDGIJ</t>
-  </si>
-  <si>
-    <t>ACDGHJ</t>
-  </si>
-  <si>
-    <t>ACDGHI</t>
-  </si>
-  <si>
-    <t>ACDGHIJ</t>
-  </si>
-  <si>
-    <t>ACDFIJ</t>
-  </si>
-  <si>
-    <t>ACDFHJ</t>
-  </si>
-  <si>
-    <t>ACDFHI</t>
-  </si>
-  <si>
-    <t>ACDFHIJ</t>
-  </si>
-  <si>
-    <t>ACDFGJ</t>
-  </si>
-  <si>
-    <t>ACDFGI</t>
-  </si>
-  <si>
-    <t>ACDFGIJ</t>
-  </si>
-  <si>
-    <t>ACDFGH</t>
-  </si>
-  <si>
-    <t>ACDFGHJ</t>
-  </si>
-  <si>
-    <t>ACDFGHI</t>
-  </si>
-  <si>
     <t>ACDFGHIJ</t>
   </si>
   <si>
-    <t>ACDEIJ</t>
-  </si>
-  <si>
-    <t>ACDEHJ</t>
-  </si>
-  <si>
-    <t>ACDEHI</t>
-  </si>
-  <si>
-    <t>ACDEHIJ</t>
-  </si>
-  <si>
-    <t>ACDEGJ</t>
-  </si>
-  <si>
-    <t>ACDEGI</t>
-  </si>
-  <si>
-    <t>ACDEGIJ</t>
-  </si>
-  <si>
-    <t>ACDEGH</t>
-  </si>
-  <si>
-    <t>ACDEGHJ</t>
-  </si>
-  <si>
-    <t>ACDEGHI</t>
-  </si>
-  <si>
     <t>ACDEGHIJ</t>
   </si>
   <si>
-    <t>ACDEFJ</t>
-  </si>
-  <si>
-    <t>ACDEFI</t>
-  </si>
-  <si>
-    <t>ACDEFIJ</t>
-  </si>
-  <si>
-    <t>ACDEFH</t>
-  </si>
-  <si>
-    <t>ACDEFHJ</t>
-  </si>
-  <si>
-    <t>ACDEFHI</t>
-  </si>
-  <si>
     <t>ACDEFHIJ</t>
   </si>
   <si>
-    <t>ACDEFG</t>
-  </si>
-  <si>
-    <t>ACDEFGJ</t>
-  </si>
-  <si>
-    <t>ACDEFGI</t>
-  </si>
-  <si>
     <t>ACDEFGIJ</t>
   </si>
   <si>
-    <t>ACDEFGH</t>
-  </si>
-  <si>
     <t>ACDEFGHJ</t>
   </si>
   <si>
     <t>ACDEFGHI</t>
   </si>
   <si>
-    <t>ABGHIJ</t>
-  </si>
-  <si>
-    <t>ABFHIJ</t>
-  </si>
-  <si>
-    <t>ABFGIJ</t>
-  </si>
-  <si>
-    <t>ABFGHJ</t>
-  </si>
-  <si>
-    <t>ABFGHI</t>
-  </si>
-  <si>
-    <t>ABFGHIJ</t>
-  </si>
-  <si>
-    <t>ABEHIJ</t>
-  </si>
-  <si>
-    <t>ABEGIJ</t>
-  </si>
-  <si>
-    <t>ABEGHJ</t>
-  </si>
-  <si>
-    <t>ABEGHI</t>
-  </si>
-  <si>
-    <t>ABEGHIJ</t>
-  </si>
-  <si>
-    <t>ABEFIJ</t>
-  </si>
-  <si>
-    <t>ABEFHJ</t>
-  </si>
-  <si>
-    <t>ABEFHI</t>
-  </si>
-  <si>
-    <t>ABEFHIJ</t>
-  </si>
-  <si>
-    <t>ABEFGJ</t>
-  </si>
-  <si>
-    <t>ABEFGI</t>
-  </si>
-  <si>
-    <t>ABEFGIJ</t>
-  </si>
-  <si>
-    <t>ABEFGH</t>
-  </si>
-  <si>
-    <t>ABEFGHJ</t>
-  </si>
-  <si>
-    <t>ABEFGHI</t>
-  </si>
-  <si>
     <t>ABEFGHIJ</t>
   </si>
   <si>
-    <t>ABDHIJ</t>
-  </si>
-  <si>
-    <t>ABDGIJ</t>
-  </si>
-  <si>
-    <t>ABDGHJ</t>
-  </si>
-  <si>
-    <t>ABDGHI</t>
-  </si>
-  <si>
-    <t>ABDGHIJ</t>
-  </si>
-  <si>
-    <t>ABDFIJ</t>
-  </si>
-  <si>
-    <t>ABDFHJ</t>
-  </si>
-  <si>
-    <t>ABDFHI</t>
-  </si>
-  <si>
-    <t>ABDFHIJ</t>
-  </si>
-  <si>
-    <t>ABDFGJ</t>
-  </si>
-  <si>
-    <t>ABDFGI</t>
-  </si>
-  <si>
-    <t>ABDFGIJ</t>
-  </si>
-  <si>
-    <t>ABDFGH</t>
-  </si>
-  <si>
-    <t>ABDFGHJ</t>
-  </si>
-  <si>
-    <t>ABDFGHI</t>
-  </si>
-  <si>
     <t>ABDFGHIJ</t>
   </si>
   <si>
-    <t>ABDEIJ</t>
-  </si>
-  <si>
-    <t>ABDEHJ</t>
-  </si>
-  <si>
-    <t>ABDEHI</t>
-  </si>
-  <si>
-    <t>ABDEHIJ</t>
-  </si>
-  <si>
-    <t>ABDEGJ</t>
-  </si>
-  <si>
-    <t>ABDEGI</t>
-  </si>
-  <si>
-    <t>ABDEGIJ</t>
-  </si>
-  <si>
-    <t>ABDEGH</t>
-  </si>
-  <si>
-    <t>ABDEGHJ</t>
-  </si>
-  <si>
-    <t>ABDEGHI</t>
-  </si>
-  <si>
     <t>ABDEGHIJ</t>
   </si>
   <si>
-    <t>ABDEFJ</t>
-  </si>
-  <si>
-    <t>ABDEFI</t>
-  </si>
-  <si>
-    <t>ABDEFIJ</t>
-  </si>
-  <si>
-    <t>ABDEFH</t>
-  </si>
-  <si>
-    <t>ABDEFHJ</t>
-  </si>
-  <si>
-    <t>ABDEFHI</t>
-  </si>
-  <si>
     <t>ABDEFHIJ</t>
   </si>
   <si>
-    <t>ABDEFG</t>
-  </si>
-  <si>
-    <t>ABDEFGJ</t>
-  </si>
-  <si>
-    <t>ABDEFGI</t>
-  </si>
-  <si>
     <t>ABDEFGIJ</t>
   </si>
   <si>
-    <t>ABDEFGH</t>
-  </si>
-  <si>
     <t>ABDEFGHJ</t>
   </si>
   <si>
     <t>ABDEFGHI</t>
   </si>
   <si>
-    <t>ABCHIJ</t>
-  </si>
-  <si>
-    <t>ABCGIJ</t>
-  </si>
-  <si>
-    <t>ABCGHJ</t>
-  </si>
-  <si>
-    <t>ABCGHI</t>
-  </si>
-  <si>
-    <t>ABCGHIJ</t>
-  </si>
-  <si>
-    <t>ABCFIJ</t>
-  </si>
-  <si>
-    <t>ABCFHJ</t>
-  </si>
-  <si>
-    <t>ABCFHI</t>
-  </si>
-  <si>
-    <t>ABCFHIJ</t>
-  </si>
-  <si>
-    <t>ABCFGJ</t>
-  </si>
-  <si>
-    <t>ABCFGI</t>
-  </si>
-  <si>
-    <t>ABCFGIJ</t>
-  </si>
-  <si>
-    <t>ABCFGH</t>
-  </si>
-  <si>
-    <t>ABCFGHJ</t>
-  </si>
-  <si>
-    <t>ABCFGHI</t>
-  </si>
-  <si>
     <t>ABCFGHIJ</t>
   </si>
   <si>
-    <t>ABCEIJ</t>
-  </si>
-  <si>
-    <t>ABCEHJ</t>
-  </si>
-  <si>
-    <t>ABCEHI</t>
-  </si>
-  <si>
-    <t>ABCEHIJ</t>
-  </si>
-  <si>
-    <t>ABCEGJ</t>
-  </si>
-  <si>
-    <t>ABCEGI</t>
-  </si>
-  <si>
-    <t>ABCEGIJ</t>
-  </si>
-  <si>
-    <t>ABCEGH</t>
-  </si>
-  <si>
-    <t>ABCEGHJ</t>
-  </si>
-  <si>
-    <t>ABCEGHI</t>
-  </si>
-  <si>
     <t>ABCEGHIJ</t>
   </si>
   <si>
-    <t>ABCEFJ</t>
-  </si>
-  <si>
-    <t>ABCEFI</t>
-  </si>
-  <si>
-    <t>ABCEFIJ</t>
-  </si>
-  <si>
-    <t>ABCEFH</t>
-  </si>
-  <si>
-    <t>ABCEFHJ</t>
-  </si>
-  <si>
-    <t>ABCEFHI</t>
-  </si>
-  <si>
     <t>ABCEFHIJ</t>
   </si>
   <si>
-    <t>ABCEFG</t>
-  </si>
-  <si>
-    <t>ABCEFGJ</t>
-  </si>
-  <si>
-    <t>ABCEFGI</t>
-  </si>
-  <si>
     <t>ABCEFGIJ</t>
   </si>
   <si>
-    <t>ABCEFGH</t>
-  </si>
-  <si>
     <t>ABCEFGHJ</t>
   </si>
   <si>
     <t>ABCEFGHI</t>
   </si>
   <si>
-    <t>ABCDIJ</t>
-  </si>
-  <si>
-    <t>ABCDHJ</t>
-  </si>
-  <si>
-    <t>ABCDHI</t>
-  </si>
-  <si>
-    <t>ABCDHIJ</t>
-  </si>
-  <si>
-    <t>ABCDGJ</t>
-  </si>
-  <si>
-    <t>ABCDGI</t>
-  </si>
-  <si>
-    <t>ABCDGIJ</t>
-  </si>
-  <si>
-    <t>ABCDGH</t>
-  </si>
-  <si>
-    <t>ABCDGHJ</t>
-  </si>
-  <si>
-    <t>ABCDGHI</t>
-  </si>
-  <si>
     <t>ABCDGHIJ</t>
   </si>
   <si>
-    <t>ABCDFJ</t>
-  </si>
-  <si>
-    <t>ABCDFI</t>
-  </si>
-  <si>
-    <t>ABCDFIJ</t>
-  </si>
-  <si>
-    <t>ABCDFH</t>
-  </si>
-  <si>
-    <t>ABCDFHJ</t>
-  </si>
-  <si>
-    <t>ABCDFHI</t>
-  </si>
-  <si>
     <t>ABCDFHIJ</t>
   </si>
   <si>
-    <t>ABCDFG</t>
-  </si>
-  <si>
-    <t>ABCDFGJ</t>
-  </si>
-  <si>
-    <t>ABCDFGI</t>
-  </si>
-  <si>
     <t>ABCDFGIJ</t>
   </si>
   <si>
-    <t>ABCDFGH</t>
-  </si>
-  <si>
     <t>ABCDFGHJ</t>
   </si>
   <si>
     <t>ABCDFGHI</t>
   </si>
   <si>
-    <t>ABCDEJ</t>
-  </si>
-  <si>
-    <t>ABCDEI</t>
-  </si>
-  <si>
-    <t>ABCDEIJ</t>
-  </si>
-  <si>
-    <t>ABCDEH</t>
-  </si>
-  <si>
-    <t>ABCDEHJ</t>
-  </si>
-  <si>
-    <t>ABCDEHI</t>
-  </si>
-  <si>
     <t>ABCDEHIJ</t>
   </si>
   <si>
-    <t>ABCDEG</t>
-  </si>
-  <si>
-    <t>ABCDEGJ</t>
-  </si>
-  <si>
-    <t>ABCDEGI</t>
-  </si>
-  <si>
     <t>ABCDEGIJ</t>
   </si>
   <si>
-    <t>ABCDEGH</t>
-  </si>
-  <si>
     <t>ABCDEGHJ</t>
   </si>
   <si>
     <t>ABCDEGHI</t>
   </si>
   <si>
-    <t>ABCDEF</t>
-  </si>
-  <si>
-    <t>ABCDEFJ</t>
-  </si>
-  <si>
-    <t>ABCDEFI</t>
-  </si>
-  <si>
     <t>ABCDEFIJ</t>
   </si>
   <si>
-    <t>ABCDEFH</t>
-  </si>
-  <si>
     <t>ABCDEFHJ</t>
   </si>
   <si>
     <t>ABCDEFHI</t>
   </si>
   <si>
-    <t>ABCDEFG</t>
-  </si>
-  <si>
     <t>ABCDEFGJ</t>
   </si>
   <si>
@@ -1230,6 +243,1353 @@
   </si>
   <si>
     <t>combination</t>
+  </si>
+  <si>
+    <t>DFGHIJKL</t>
+  </si>
+  <si>
+    <t>DEGHIJKL</t>
+  </si>
+  <si>
+    <t>DEFHIJKL</t>
+  </si>
+  <si>
+    <t>DEFGIJKL</t>
+  </si>
+  <si>
+    <t>DEFGHJKL</t>
+  </si>
+  <si>
+    <t>DEFGHIKL</t>
+  </si>
+  <si>
+    <t>DEFGHIJL</t>
+  </si>
+  <si>
+    <t>DEFGHIJK</t>
+  </si>
+  <si>
+    <t>CFGHIJKL</t>
+  </si>
+  <si>
+    <t>CEGHIJKL</t>
+  </si>
+  <si>
+    <t>CEFHIJKL</t>
+  </si>
+  <si>
+    <t>CEFGIJKL</t>
+  </si>
+  <si>
+    <t>CEFGHJKL</t>
+  </si>
+  <si>
+    <t>CEFGHIKL</t>
+  </si>
+  <si>
+    <t>CEFGHIJL</t>
+  </si>
+  <si>
+    <t>CEFGHIJK</t>
+  </si>
+  <si>
+    <t>CDGHIJKL</t>
+  </si>
+  <si>
+    <t>CDFHIJKL</t>
+  </si>
+  <si>
+    <t>CDFGIJKL</t>
+  </si>
+  <si>
+    <t>CDFGHJKL</t>
+  </si>
+  <si>
+    <t>CDFGHIKL</t>
+  </si>
+  <si>
+    <t>CDFGHIJL</t>
+  </si>
+  <si>
+    <t>CDFGHIJK</t>
+  </si>
+  <si>
+    <t>CDEHIJKL</t>
+  </si>
+  <si>
+    <t>CDEGIJKL</t>
+  </si>
+  <si>
+    <t>CDEGHJKL</t>
+  </si>
+  <si>
+    <t>CDEGHIKL</t>
+  </si>
+  <si>
+    <t>CDEGHIJL</t>
+  </si>
+  <si>
+    <t>CDEGHIJK</t>
+  </si>
+  <si>
+    <t>CDEFIJKL</t>
+  </si>
+  <si>
+    <t>CDEFHJKL</t>
+  </si>
+  <si>
+    <t>CDEFHIKL</t>
+  </si>
+  <si>
+    <t>CDEFHIJL</t>
+  </si>
+  <si>
+    <t>CDEFHIJK</t>
+  </si>
+  <si>
+    <t>CDEFGJKL</t>
+  </si>
+  <si>
+    <t>CDEFGIKL</t>
+  </si>
+  <si>
+    <t>CDEFGIJL</t>
+  </si>
+  <si>
+    <t>CDEFGIJK</t>
+  </si>
+  <si>
+    <t>CDEFGHKL</t>
+  </si>
+  <si>
+    <t>CDEFGHJL</t>
+  </si>
+  <si>
+    <t>CDEFGHJK</t>
+  </si>
+  <si>
+    <t>CDEFGHIL</t>
+  </si>
+  <si>
+    <t>CDEFGHIK</t>
+  </si>
+  <si>
+    <t>BFGHIJKL</t>
+  </si>
+  <si>
+    <t>BEGHIJKL</t>
+  </si>
+  <si>
+    <t>BEFHIJKL</t>
+  </si>
+  <si>
+    <t>BEFGIJKL</t>
+  </si>
+  <si>
+    <t>BEFGHJKL</t>
+  </si>
+  <si>
+    <t>BEFGHIKL</t>
+  </si>
+  <si>
+    <t>BEFGHIJL</t>
+  </si>
+  <si>
+    <t>BEFGHIJK</t>
+  </si>
+  <si>
+    <t>BDGHIJKL</t>
+  </si>
+  <si>
+    <t>BDFHIJKL</t>
+  </si>
+  <si>
+    <t>BDFGIJKL</t>
+  </si>
+  <si>
+    <t>BDFGHJKL</t>
+  </si>
+  <si>
+    <t>BDFGHIKL</t>
+  </si>
+  <si>
+    <t>BDFGHIJL</t>
+  </si>
+  <si>
+    <t>BDFGHIJK</t>
+  </si>
+  <si>
+    <t>BDEHIJKL</t>
+  </si>
+  <si>
+    <t>BDEGIJKL</t>
+  </si>
+  <si>
+    <t>BDEGHJKL</t>
+  </si>
+  <si>
+    <t>BDEGHIKL</t>
+  </si>
+  <si>
+    <t>BDEGHIJL</t>
+  </si>
+  <si>
+    <t>BDEGHIJK</t>
+  </si>
+  <si>
+    <t>BDEFIJKL</t>
+  </si>
+  <si>
+    <t>BDEFHJKL</t>
+  </si>
+  <si>
+    <t>BDEFHIKL</t>
+  </si>
+  <si>
+    <t>BDEFHIJL</t>
+  </si>
+  <si>
+    <t>BDEFHIJK</t>
+  </si>
+  <si>
+    <t>BDEFGJKL</t>
+  </si>
+  <si>
+    <t>BDEFGIKL</t>
+  </si>
+  <si>
+    <t>BDEFGIJL</t>
+  </si>
+  <si>
+    <t>BDEFGIJK</t>
+  </si>
+  <si>
+    <t>BDEFGHKL</t>
+  </si>
+  <si>
+    <t>BDEFGHJL</t>
+  </si>
+  <si>
+    <t>BDEFGHJK</t>
+  </si>
+  <si>
+    <t>BDEFGHIL</t>
+  </si>
+  <si>
+    <t>BDEFGHIK</t>
+  </si>
+  <si>
+    <t>BCGHIJKL</t>
+  </si>
+  <si>
+    <t>BCFHIJKL</t>
+  </si>
+  <si>
+    <t>BCFGIJKL</t>
+  </si>
+  <si>
+    <t>BCFGHJKL</t>
+  </si>
+  <si>
+    <t>BCFGHIKL</t>
+  </si>
+  <si>
+    <t>BCFGHIJL</t>
+  </si>
+  <si>
+    <t>BCFGHIJK</t>
+  </si>
+  <si>
+    <t>BCEHIJKL</t>
+  </si>
+  <si>
+    <t>BCEGIJKL</t>
+  </si>
+  <si>
+    <t>BCEGHJKL</t>
+  </si>
+  <si>
+    <t>BCEGHIKL</t>
+  </si>
+  <si>
+    <t>BCEGHIJL</t>
+  </si>
+  <si>
+    <t>BCEGHIJK</t>
+  </si>
+  <si>
+    <t>BCEFIJKL</t>
+  </si>
+  <si>
+    <t>BCEFHJKL</t>
+  </si>
+  <si>
+    <t>BCEFHIKL</t>
+  </si>
+  <si>
+    <t>BCEFHIJL</t>
+  </si>
+  <si>
+    <t>BCEFHIJK</t>
+  </si>
+  <si>
+    <t>BCEFGJKL</t>
+  </si>
+  <si>
+    <t>BCEFGIKL</t>
+  </si>
+  <si>
+    <t>BCEFGIJL</t>
+  </si>
+  <si>
+    <t>BCEFGIJK</t>
+  </si>
+  <si>
+    <t>BCEFGHKL</t>
+  </si>
+  <si>
+    <t>BCEFGHJL</t>
+  </si>
+  <si>
+    <t>BCEFGHJK</t>
+  </si>
+  <si>
+    <t>BCEFGHIL</t>
+  </si>
+  <si>
+    <t>BCEFGHIK</t>
+  </si>
+  <si>
+    <t>BCDHIJKL</t>
+  </si>
+  <si>
+    <t>BCDGIJKL</t>
+  </si>
+  <si>
+    <t>BCDGHJKL</t>
+  </si>
+  <si>
+    <t>BCDGHIKL</t>
+  </si>
+  <si>
+    <t>BCDGHIJL</t>
+  </si>
+  <si>
+    <t>BCDGHIJK</t>
+  </si>
+  <si>
+    <t>BCDFIJKL</t>
+  </si>
+  <si>
+    <t>BCDFHJKL</t>
+  </si>
+  <si>
+    <t>BCDFHIKL</t>
+  </si>
+  <si>
+    <t>BCDFHIJL</t>
+  </si>
+  <si>
+    <t>BCDFHIJK</t>
+  </si>
+  <si>
+    <t>BCDFGJKL</t>
+  </si>
+  <si>
+    <t>BCDFGIKL</t>
+  </si>
+  <si>
+    <t>BCDFGIJL</t>
+  </si>
+  <si>
+    <t>BCDFGIJK</t>
+  </si>
+  <si>
+    <t>BCDFGHKL</t>
+  </si>
+  <si>
+    <t>BCDFGHJL</t>
+  </si>
+  <si>
+    <t>BCDFGHJK</t>
+  </si>
+  <si>
+    <t>BCDFGHIL</t>
+  </si>
+  <si>
+    <t>BCDFGHIK</t>
+  </si>
+  <si>
+    <t>BCDEIJKL</t>
+  </si>
+  <si>
+    <t>BCDEHJKL</t>
+  </si>
+  <si>
+    <t>BCDEHIKL</t>
+  </si>
+  <si>
+    <t>BCDEHIJL</t>
+  </si>
+  <si>
+    <t>BCDEHIJK</t>
+  </si>
+  <si>
+    <t>BCDEGJKL</t>
+  </si>
+  <si>
+    <t>BCDEGIKL</t>
+  </si>
+  <si>
+    <t>BCDEGIJL</t>
+  </si>
+  <si>
+    <t>BCDEGIJK</t>
+  </si>
+  <si>
+    <t>BCDEGHKL</t>
+  </si>
+  <si>
+    <t>BCDEGHJL</t>
+  </si>
+  <si>
+    <t>BCDEGHJK</t>
+  </si>
+  <si>
+    <t>BCDEGHIL</t>
+  </si>
+  <si>
+    <t>BCDEGHIK</t>
+  </si>
+  <si>
+    <t>BCDEFJKL</t>
+  </si>
+  <si>
+    <t>BCDEFIKL</t>
+  </si>
+  <si>
+    <t>BCDEFIJL</t>
+  </si>
+  <si>
+    <t>BCDEFIJK</t>
+  </si>
+  <si>
+    <t>BCDEFHKL</t>
+  </si>
+  <si>
+    <t>BCDEFHJL</t>
+  </si>
+  <si>
+    <t>BCDEFHJK</t>
+  </si>
+  <si>
+    <t>BCDEFHIL</t>
+  </si>
+  <si>
+    <t>BCDEFHIK</t>
+  </si>
+  <si>
+    <t>BCDEFGKL</t>
+  </si>
+  <si>
+    <t>BCDEFGJL</t>
+  </si>
+  <si>
+    <t>BCDEFGJK</t>
+  </si>
+  <si>
+    <t>BCDEFGIL</t>
+  </si>
+  <si>
+    <t>BCDEFGIK</t>
+  </si>
+  <si>
+    <t>BCDEFGHL</t>
+  </si>
+  <si>
+    <t>BCDEFGHK</t>
+  </si>
+  <si>
+    <t>AFGHIJKL</t>
+  </si>
+  <si>
+    <t>AEGHIJKL</t>
+  </si>
+  <si>
+    <t>AEFHIJKL</t>
+  </si>
+  <si>
+    <t>AEFGIJKL</t>
+  </si>
+  <si>
+    <t>AEFGHJKL</t>
+  </si>
+  <si>
+    <t>AEFGHIKL</t>
+  </si>
+  <si>
+    <t>AEFGHIJL</t>
+  </si>
+  <si>
+    <t>AEFGHIJK</t>
+  </si>
+  <si>
+    <t>ADGHIJKL</t>
+  </si>
+  <si>
+    <t>ADFHIJKL</t>
+  </si>
+  <si>
+    <t>ADFGIJKL</t>
+  </si>
+  <si>
+    <t>ADFGHJKL</t>
+  </si>
+  <si>
+    <t>ADFGHIKL</t>
+  </si>
+  <si>
+    <t>ADFGHIJL</t>
+  </si>
+  <si>
+    <t>ADFGHIJK</t>
+  </si>
+  <si>
+    <t>ADEHIJKL</t>
+  </si>
+  <si>
+    <t>ADEGIJKL</t>
+  </si>
+  <si>
+    <t>ADEGHJKL</t>
+  </si>
+  <si>
+    <t>ADEGHIKL</t>
+  </si>
+  <si>
+    <t>ADEGHIJL</t>
+  </si>
+  <si>
+    <t>ADEGHIJK</t>
+  </si>
+  <si>
+    <t>ADEFIJKL</t>
+  </si>
+  <si>
+    <t>ADEFHJKL</t>
+  </si>
+  <si>
+    <t>ADEFHIKL</t>
+  </si>
+  <si>
+    <t>ADEFHIJL</t>
+  </si>
+  <si>
+    <t>ADEFHIJK</t>
+  </si>
+  <si>
+    <t>ADEFGJKL</t>
+  </si>
+  <si>
+    <t>ADEFGIKL</t>
+  </si>
+  <si>
+    <t>ADEFGIJL</t>
+  </si>
+  <si>
+    <t>ADEFGIJK</t>
+  </si>
+  <si>
+    <t>ADEFGHKL</t>
+  </si>
+  <si>
+    <t>ADEFGHJL</t>
+  </si>
+  <si>
+    <t>ADEFGHJK</t>
+  </si>
+  <si>
+    <t>ADEFGHIL</t>
+  </si>
+  <si>
+    <t>ADEFGHIK</t>
+  </si>
+  <si>
+    <t>ACGHIJKL</t>
+  </si>
+  <si>
+    <t>ACFHIJKL</t>
+  </si>
+  <si>
+    <t>ACFGIJKL</t>
+  </si>
+  <si>
+    <t>ACFGHJKL</t>
+  </si>
+  <si>
+    <t>ACFGHIKL</t>
+  </si>
+  <si>
+    <t>ACFGHIJL</t>
+  </si>
+  <si>
+    <t>ACFGHIJK</t>
+  </si>
+  <si>
+    <t>ACEHIJKL</t>
+  </si>
+  <si>
+    <t>ACEGIJKL</t>
+  </si>
+  <si>
+    <t>ACEGHJKL</t>
+  </si>
+  <si>
+    <t>ACEGHIKL</t>
+  </si>
+  <si>
+    <t>ACEGHIJL</t>
+  </si>
+  <si>
+    <t>ACEGHIJK</t>
+  </si>
+  <si>
+    <t>ACEFIJKL</t>
+  </si>
+  <si>
+    <t>ACEFHJKL</t>
+  </si>
+  <si>
+    <t>ACEFHIKL</t>
+  </si>
+  <si>
+    <t>ACEFHIJL</t>
+  </si>
+  <si>
+    <t>ACEFHIJK</t>
+  </si>
+  <si>
+    <t>ACEFGJKL</t>
+  </si>
+  <si>
+    <t>ACEFGIKL</t>
+  </si>
+  <si>
+    <t>ACEFGIJL</t>
+  </si>
+  <si>
+    <t>ACEFGIJK</t>
+  </si>
+  <si>
+    <t>ACEFGHKL</t>
+  </si>
+  <si>
+    <t>ACEFGHJL</t>
+  </si>
+  <si>
+    <t>ACEFGHJK</t>
+  </si>
+  <si>
+    <t>ACEFGHIL</t>
+  </si>
+  <si>
+    <t>ACEFGHIK</t>
+  </si>
+  <si>
+    <t>ACDHIJKL</t>
+  </si>
+  <si>
+    <t>ACDGIJKL</t>
+  </si>
+  <si>
+    <t>ACDGHJKL</t>
+  </si>
+  <si>
+    <t>ACDGHIKL</t>
+  </si>
+  <si>
+    <t>ACDGHIJL</t>
+  </si>
+  <si>
+    <t>ACDGHIJK</t>
+  </si>
+  <si>
+    <t>ACDFIJKL</t>
+  </si>
+  <si>
+    <t>ACDFHJKL</t>
+  </si>
+  <si>
+    <t>ACDFHIKL</t>
+  </si>
+  <si>
+    <t>ACDFHIJL</t>
+  </si>
+  <si>
+    <t>ACDFHIJK</t>
+  </si>
+  <si>
+    <t>ACDFGJKL</t>
+  </si>
+  <si>
+    <t>ACDFGIKL</t>
+  </si>
+  <si>
+    <t>ACDFGIJL</t>
+  </si>
+  <si>
+    <t>ACDFGIJK</t>
+  </si>
+  <si>
+    <t>ACDFGHKL</t>
+  </si>
+  <si>
+    <t>ACDFGHJL</t>
+  </si>
+  <si>
+    <t>ACDFGHJK</t>
+  </si>
+  <si>
+    <t>ACDFGHIL</t>
+  </si>
+  <si>
+    <t>ACDFGHIK</t>
+  </si>
+  <si>
+    <t>ACDEIJKL</t>
+  </si>
+  <si>
+    <t>ACDEHJKL</t>
+  </si>
+  <si>
+    <t>ACDEHIKL</t>
+  </si>
+  <si>
+    <t>ACDEHIJL</t>
+  </si>
+  <si>
+    <t>ACDEHIJK</t>
+  </si>
+  <si>
+    <t>ACDEGJKL</t>
+  </si>
+  <si>
+    <t>ACDEGIKL</t>
+  </si>
+  <si>
+    <t>ACDEGIJL</t>
+  </si>
+  <si>
+    <t>ACDEGIJK</t>
+  </si>
+  <si>
+    <t>ACDEGHKL</t>
+  </si>
+  <si>
+    <t>ACDEGHJL</t>
+  </si>
+  <si>
+    <t>ACDEGHJK</t>
+  </si>
+  <si>
+    <t>ACDEGHIL</t>
+  </si>
+  <si>
+    <t>ACDEGHIK</t>
+  </si>
+  <si>
+    <t>ACDEFJKL</t>
+  </si>
+  <si>
+    <t>ACDEFIKL</t>
+  </si>
+  <si>
+    <t>ACDEFIJL</t>
+  </si>
+  <si>
+    <t>ACDEFIJK</t>
+  </si>
+  <si>
+    <t>ACDEFHKL</t>
+  </si>
+  <si>
+    <t>ACDEFHJL</t>
+  </si>
+  <si>
+    <t>ACDEFHJK</t>
+  </si>
+  <si>
+    <t>ACDEFHIL</t>
+  </si>
+  <si>
+    <t>ACDEFHIK</t>
+  </si>
+  <si>
+    <t>ACDEFGKL</t>
+  </si>
+  <si>
+    <t>ACDEFGJL</t>
+  </si>
+  <si>
+    <t>ACDEFGJK</t>
+  </si>
+  <si>
+    <t>ACDEFGIL</t>
+  </si>
+  <si>
+    <t>ACDEFGIK</t>
+  </si>
+  <si>
+    <t>ACDEFGHL</t>
+  </si>
+  <si>
+    <t>ACDEFGHK</t>
+  </si>
+  <si>
+    <t>ABGHIJKL</t>
+  </si>
+  <si>
+    <t>ABFHIJKL</t>
+  </si>
+  <si>
+    <t>ABFGIJKL</t>
+  </si>
+  <si>
+    <t>ABFGHJKL</t>
+  </si>
+  <si>
+    <t>ABFGHIKL</t>
+  </si>
+  <si>
+    <t>ABFGHIJL</t>
+  </si>
+  <si>
+    <t>ABFGHIJK</t>
+  </si>
+  <si>
+    <t>ABEHIJKL</t>
+  </si>
+  <si>
+    <t>ABEGIJKL</t>
+  </si>
+  <si>
+    <t>ABEGHJKL</t>
+  </si>
+  <si>
+    <t>ABEGHIKL</t>
+  </si>
+  <si>
+    <t>ABEGHIJL</t>
+  </si>
+  <si>
+    <t>ABEGHIJK</t>
+  </si>
+  <si>
+    <t>ABEFIJKL</t>
+  </si>
+  <si>
+    <t>ABEFHJKL</t>
+  </si>
+  <si>
+    <t>ABEFHIKL</t>
+  </si>
+  <si>
+    <t>ABEFHIJL</t>
+  </si>
+  <si>
+    <t>ABEFHIJK</t>
+  </si>
+  <si>
+    <t>ABEFGJKL</t>
+  </si>
+  <si>
+    <t>ABEFGIKL</t>
+  </si>
+  <si>
+    <t>ABEFGIJL</t>
+  </si>
+  <si>
+    <t>ABEFGIJK</t>
+  </si>
+  <si>
+    <t>ABEFGHKL</t>
+  </si>
+  <si>
+    <t>ABEFGHJL</t>
+  </si>
+  <si>
+    <t>ABEFGHJK</t>
+  </si>
+  <si>
+    <t>ABEFGHIL</t>
+  </si>
+  <si>
+    <t>ABEFGHIK</t>
+  </si>
+  <si>
+    <t>ABDHIJKL</t>
+  </si>
+  <si>
+    <t>ABDGIJKL</t>
+  </si>
+  <si>
+    <t>ABDGHJKL</t>
+  </si>
+  <si>
+    <t>ABDGHIKL</t>
+  </si>
+  <si>
+    <t>ABDGHIJL</t>
+  </si>
+  <si>
+    <t>ABDGHIJK</t>
+  </si>
+  <si>
+    <t>ABDFIJKL</t>
+  </si>
+  <si>
+    <t>ABDFHJKL</t>
+  </si>
+  <si>
+    <t>ABDFHIKL</t>
+  </si>
+  <si>
+    <t>ABDFHIJL</t>
+  </si>
+  <si>
+    <t>ABDFHIJK</t>
+  </si>
+  <si>
+    <t>ABDFGJKL</t>
+  </si>
+  <si>
+    <t>ABDFGIKL</t>
+  </si>
+  <si>
+    <t>ABDFGIJL</t>
+  </si>
+  <si>
+    <t>ABDFGIJK</t>
+  </si>
+  <si>
+    <t>ABDFGHKL</t>
+  </si>
+  <si>
+    <t>ABDFGHJL</t>
+  </si>
+  <si>
+    <t>ABDFGHJK</t>
+  </si>
+  <si>
+    <t>ABDFGHIL</t>
+  </si>
+  <si>
+    <t>ABDFGHIK</t>
+  </si>
+  <si>
+    <t>ABDEIJKL</t>
+  </si>
+  <si>
+    <t>ABDEHJKL</t>
+  </si>
+  <si>
+    <t>ABDEHIKL</t>
+  </si>
+  <si>
+    <t>ABDEHIJL</t>
+  </si>
+  <si>
+    <t>ABDEHIJK</t>
+  </si>
+  <si>
+    <t>ABDEGJKL</t>
+  </si>
+  <si>
+    <t>ABDEGIKL</t>
+  </si>
+  <si>
+    <t>ABDEGIJL</t>
+  </si>
+  <si>
+    <t>ABDEGIJK</t>
+  </si>
+  <si>
+    <t>ABDEGHKL</t>
+  </si>
+  <si>
+    <t>ABDEGHJL</t>
+  </si>
+  <si>
+    <t>ABDEGHJK</t>
+  </si>
+  <si>
+    <t>ABDEGHIL</t>
+  </si>
+  <si>
+    <t>ABDEGHIK</t>
+  </si>
+  <si>
+    <t>ABDEFJKL</t>
+  </si>
+  <si>
+    <t>ABDEFIKL</t>
+  </si>
+  <si>
+    <t>ABDEFIJL</t>
+  </si>
+  <si>
+    <t>ABDEFIJK</t>
+  </si>
+  <si>
+    <t>ABDEFHKL</t>
+  </si>
+  <si>
+    <t>ABDEFHJL</t>
+  </si>
+  <si>
+    <t>ABDEFHJK</t>
+  </si>
+  <si>
+    <t>ABDEFHIL</t>
+  </si>
+  <si>
+    <t>ABDEFHIK</t>
+  </si>
+  <si>
+    <t>ABDEFGKL</t>
+  </si>
+  <si>
+    <t>ABDEFGJL</t>
+  </si>
+  <si>
+    <t>ABDEFGJK</t>
+  </si>
+  <si>
+    <t>ABDEFGIL</t>
+  </si>
+  <si>
+    <t>ABDEFGIK</t>
+  </si>
+  <si>
+    <t>ABDEFGHL</t>
+  </si>
+  <si>
+    <t>ABDEFGHK</t>
+  </si>
+  <si>
+    <t>ABCHIJKL</t>
+  </si>
+  <si>
+    <t>ABCGIJKL</t>
+  </si>
+  <si>
+    <t>ABCGHJKL</t>
+  </si>
+  <si>
+    <t>ABCGHIKL</t>
+  </si>
+  <si>
+    <t>ABCGHIJL</t>
+  </si>
+  <si>
+    <t>ABCGHIJK</t>
+  </si>
+  <si>
+    <t>ABCFIJKL</t>
+  </si>
+  <si>
+    <t>ABCFHJKL</t>
+  </si>
+  <si>
+    <t>ABCFHIKL</t>
+  </si>
+  <si>
+    <t>ABCFHIJL</t>
+  </si>
+  <si>
+    <t>ABCFHIJK</t>
+  </si>
+  <si>
+    <t>ABCFGJKL</t>
+  </si>
+  <si>
+    <t>ABCFGIKL</t>
+  </si>
+  <si>
+    <t>ABCFGIJL</t>
+  </si>
+  <si>
+    <t>ABCFGIJK</t>
+  </si>
+  <si>
+    <t>ABCFGHKL</t>
+  </si>
+  <si>
+    <t>ABCFGHJL</t>
+  </si>
+  <si>
+    <t>ABCFGHJK</t>
+  </si>
+  <si>
+    <t>ABCFGHIL</t>
+  </si>
+  <si>
+    <t>ABCFGHIK</t>
+  </si>
+  <si>
+    <t>ABCEIJKL</t>
+  </si>
+  <si>
+    <t>ABCEHJKL</t>
+  </si>
+  <si>
+    <t>ABCEHIKL</t>
+  </si>
+  <si>
+    <t>ABCEHIJL</t>
+  </si>
+  <si>
+    <t>ABCEHIJK</t>
+  </si>
+  <si>
+    <t>ABCEGJKL</t>
+  </si>
+  <si>
+    <t>ABCEGIKL</t>
+  </si>
+  <si>
+    <t>ABCEGIJL</t>
+  </si>
+  <si>
+    <t>ABCEGIJK</t>
+  </si>
+  <si>
+    <t>ABCEGHKL</t>
+  </si>
+  <si>
+    <t>ABCEGHJL</t>
+  </si>
+  <si>
+    <t>ABCEGHJK</t>
+  </si>
+  <si>
+    <t>ABCEGHIL</t>
+  </si>
+  <si>
+    <t>ABCEGHIK</t>
+  </si>
+  <si>
+    <t>ABCEFJKL</t>
+  </si>
+  <si>
+    <t>ABCEFIKL</t>
+  </si>
+  <si>
+    <t>ABCEFIJL</t>
+  </si>
+  <si>
+    <t>ABCEFIJK</t>
+  </si>
+  <si>
+    <t>ABCEFHKL</t>
+  </si>
+  <si>
+    <t>ABCEFHJL</t>
+  </si>
+  <si>
+    <t>ABCEFHJK</t>
+  </si>
+  <si>
+    <t>ABCEFHIL</t>
+  </si>
+  <si>
+    <t>ABCEFHIK</t>
+  </si>
+  <si>
+    <t>ABCEFGKL</t>
+  </si>
+  <si>
+    <t>ABCEFGJL</t>
+  </si>
+  <si>
+    <t>ABCEFGJK</t>
+  </si>
+  <si>
+    <t>ABCEFGIL</t>
+  </si>
+  <si>
+    <t>ABCEFGIK</t>
+  </si>
+  <si>
+    <t>ABCEFGHL</t>
+  </si>
+  <si>
+    <t>ABCEFGHK</t>
+  </si>
+  <si>
+    <t>ABCDIJKL</t>
+  </si>
+  <si>
+    <t>ABCDHJKL</t>
+  </si>
+  <si>
+    <t>ABCDHIKL</t>
+  </si>
+  <si>
+    <t>ABCDHIJL</t>
+  </si>
+  <si>
+    <t>ABCDHIJK</t>
+  </si>
+  <si>
+    <t>ABCDGJKL</t>
+  </si>
+  <si>
+    <t>ABCDGIKL</t>
+  </si>
+  <si>
+    <t>ABCDGIJL</t>
+  </si>
+  <si>
+    <t>ABCDGIJK</t>
+  </si>
+  <si>
+    <t>ABCDGHKL</t>
+  </si>
+  <si>
+    <t>ABCDGHJL</t>
+  </si>
+  <si>
+    <t>ABCDGHJK</t>
+  </si>
+  <si>
+    <t>ABCDGHIL</t>
+  </si>
+  <si>
+    <t>ABCDGHIK</t>
+  </si>
+  <si>
+    <t>ABCDFJKL</t>
+  </si>
+  <si>
+    <t>ABCDFIKL</t>
+  </si>
+  <si>
+    <t>ABCDFIJL</t>
+  </si>
+  <si>
+    <t>ABCDFIJK</t>
+  </si>
+  <si>
+    <t>ABCDFHKL</t>
+  </si>
+  <si>
+    <t>ABCDFHJL</t>
+  </si>
+  <si>
+    <t>ABCDFHJK</t>
+  </si>
+  <si>
+    <t>ABCDFHIL</t>
+  </si>
+  <si>
+    <t>ABCDFHIK</t>
+  </si>
+  <si>
+    <t>ABCDFGKL</t>
+  </si>
+  <si>
+    <t>ABCDFGJL</t>
+  </si>
+  <si>
+    <t>ABCDFGJK</t>
+  </si>
+  <si>
+    <t>ABCDFGIL</t>
+  </si>
+  <si>
+    <t>ABCDFGIK</t>
+  </si>
+  <si>
+    <t>ABCDFGHL</t>
+  </si>
+  <si>
+    <t>ABCDFGHK</t>
+  </si>
+  <si>
+    <t>ABCDEJKL</t>
+  </si>
+  <si>
+    <t>ABCDEIKL</t>
+  </si>
+  <si>
+    <t>ABCDEIJL</t>
+  </si>
+  <si>
+    <t>ABCDEIJK</t>
+  </si>
+  <si>
+    <t>ABCDEHKL</t>
+  </si>
+  <si>
+    <t>ABCDEHJL</t>
+  </si>
+  <si>
+    <t>ABCDEHJK</t>
+  </si>
+  <si>
+    <t>ABCDEHIL</t>
+  </si>
+  <si>
+    <t>ABCDEHIK</t>
+  </si>
+  <si>
+    <t>ABCDEGKL</t>
+  </si>
+  <si>
+    <t>ABCDEGJL</t>
+  </si>
+  <si>
+    <t>ABCDEGJK</t>
+  </si>
+  <si>
+    <t>ABCDEGIL</t>
+  </si>
+  <si>
+    <t>ABCDEGIK</t>
+  </si>
+  <si>
+    <t>ABCDEGHL</t>
+  </si>
+  <si>
+    <t>ABCDEGHK</t>
+  </si>
+  <si>
+    <t>ABCDEFKL</t>
+  </si>
+  <si>
+    <t>ABCDEFJL</t>
+  </si>
+  <si>
+    <t>ABCDEFJK</t>
+  </si>
+  <si>
+    <t>ABCDEFIL</t>
+  </si>
+  <si>
+    <t>ABCDEFIK</t>
+  </si>
+  <si>
+    <t>ABCDEFHL</t>
+  </si>
+  <si>
+    <t>ABCDEFHK</t>
+  </si>
+  <si>
+    <t>ABCDEFGL</t>
+  </si>
+  <si>
+    <t>ABCDEFGK</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1969,7 @@
         <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>396</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1673,7 +2033,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -1705,7 +2065,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -1737,7 +2097,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -1769,7 +2129,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -1801,7 +2161,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -1833,7 +2193,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -1865,7 +2225,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -1897,7 +2257,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -1929,7 +2289,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -1961,7 +2321,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -1993,7 +2353,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -2025,7 +2385,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
@@ -2057,7 +2417,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -2089,7 +2449,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
@@ -2121,7 +2481,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -2153,7 +2513,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
@@ -2185,7 +2545,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -2217,7 +2577,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
         <v>17</v>
@@ -2249,7 +2609,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
@@ -2281,7 +2641,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
@@ -2313,7 +2673,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -2345,7 +2705,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -2377,7 +2737,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -2409,7 +2769,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
@@ -2441,7 +2801,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
@@ -2473,7 +2833,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
@@ -2505,7 +2865,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
@@ -2537,7 +2897,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
@@ -2569,7 +2929,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
@@ -2601,7 +2961,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
@@ -2633,7 +2993,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
         <v>17</v>
@@ -2665,7 +3025,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
         <v>17</v>
@@ -2697,7 +3057,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
@@ -2729,7 +3089,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
         <v>17</v>
@@ -2761,7 +3121,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
@@ -2793,7 +3153,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
@@ -2825,7 +3185,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
@@ -2857,7 +3217,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
@@ -2889,7 +3249,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
@@ -2921,7 +3281,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
@@ -2953,7 +3313,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
@@ -2985,7 +3345,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="C44" t="s">
         <v>17</v>
@@ -3017,7 +3377,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
@@ -3049,7 +3409,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
@@ -3081,7 +3441,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -3113,7 +3473,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
@@ -3145,7 +3505,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
@@ -3177,7 +3537,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
@@ -3209,7 +3569,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="C51" t="s">
         <v>8</v>
@@ -3241,7 +3601,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
         <v>8</v>
@@ -3273,7 +3633,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="C53" t="s">
         <v>8</v>
@@ -3305,7 +3665,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
@@ -3337,7 +3697,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
@@ -3369,7 +3729,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -3401,7 +3761,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
@@ -3433,7 +3793,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
@@ -3465,7 +3825,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
@@ -3497,7 +3857,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
@@ -3529,7 +3889,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
@@ -3561,7 +3921,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
@@ -3593,7 +3953,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
@@ -3625,7 +3985,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
@@ -3657,7 +4017,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="C65" t="s">
         <v>8</v>
@@ -3689,7 +4049,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C66" t="s">
         <v>8</v>
@@ -3721,7 +4081,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="C67" t="s">
         <v>8</v>
@@ -3753,7 +4113,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="C68" t="s">
         <v>8</v>
@@ -3785,7 +4145,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="C69" t="s">
         <v>8</v>
@@ -3817,7 +4177,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="C70" t="s">
         <v>8</v>
@@ -3849,7 +4209,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
@@ -3881,7 +4241,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="C72" t="s">
         <v>8</v>
@@ -3913,7 +4273,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="C73" t="s">
         <v>8</v>
@@ -3945,7 +4305,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="C74" t="s">
         <v>8</v>
@@ -3977,7 +4337,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="C75" t="s">
         <v>8</v>
@@ -4009,7 +4369,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="C76" t="s">
         <v>8</v>
@@ -4041,7 +4401,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="C77" t="s">
         <v>8</v>
@@ -4073,7 +4433,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
@@ -4105,7 +4465,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
@@ -4137,7 +4497,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="C80" t="s">
         <v>8</v>
@@ -4169,7 +4529,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="C81" t="s">
         <v>8</v>
@@ -4201,7 +4561,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="C82" t="s">
         <v>12</v>
@@ -4233,7 +4593,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="C83" t="s">
         <v>12</v>
@@ -4265,7 +4625,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="C84" t="s">
         <v>12</v>
@@ -4297,7 +4657,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="C85" t="s">
         <v>10</v>
@@ -4329,7 +4689,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="C86" t="s">
         <v>12</v>
@@ -4361,7 +4721,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="C87" t="s">
         <v>12</v>
@@ -4393,7 +4753,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="C88" t="s">
         <v>12</v>
@@ -4425,7 +4785,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="C89" t="s">
         <v>12</v>
@@ -4457,7 +4817,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="C90" t="s">
         <v>8</v>
@@ -4489,7 +4849,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="C91" t="s">
         <v>8</v>
@@ -4521,7 +4881,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="C92" t="s">
         <v>8</v>
@@ -4553,7 +4913,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="C93" t="s">
         <v>8</v>
@@ -4585,7 +4945,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="C94" t="s">
         <v>8</v>
@@ -4617,7 +4977,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="C95" t="s">
         <v>8</v>
@@ -4649,7 +5009,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="C96" t="s">
         <v>8</v>
@@ -4681,7 +5041,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="C97" t="s">
         <v>8</v>
@@ -4713,7 +5073,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="C98" t="s">
         <v>8</v>
@@ -4745,7 +5105,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="C99" t="s">
         <v>8</v>
@@ -4777,7 +5137,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="C100" t="s">
         <v>8</v>
@@ -4809,7 +5169,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="C101" t="s">
         <v>8</v>
@@ -4841,7 +5201,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="C102" t="s">
         <v>8</v>
@@ -4873,7 +5233,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="C103" t="s">
         <v>8</v>
@@ -4905,7 +5265,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="C104" t="s">
         <v>8</v>
@@ -4937,7 +5297,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="C105" t="s">
         <v>8</v>
@@ -4969,7 +5329,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="C106" t="s">
         <v>12</v>
@@ -5001,7 +5361,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="C107" t="s">
         <v>12</v>
@@ -5033,7 +5393,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="C108" t="s">
         <v>8</v>
@@ -5065,7 +5425,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="C109" t="s">
         <v>8</v>
@@ -5097,7 +5457,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="C110" t="s">
         <v>12</v>
@@ -5129,7 +5489,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="C111" t="s">
         <v>12</v>
@@ -5161,7 +5521,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>174</v>
       </c>
       <c r="C112" t="s">
         <v>10</v>
@@ -5193,7 +5553,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="C113" t="s">
         <v>12</v>
@@ -5225,7 +5585,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="C114" t="s">
         <v>12</v>
@@ -5257,7 +5617,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="C115" t="s">
         <v>12</v>
@@ -5289,7 +5649,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="C116" t="s">
         <v>12</v>
@@ -5321,7 +5681,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="C117" t="s">
         <v>17</v>
@@ -5353,7 +5713,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>115</v>
+        <v>180</v>
       </c>
       <c r="C118" t="s">
         <v>17</v>
@@ -5385,7 +5745,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>116</v>
+        <v>181</v>
       </c>
       <c r="C119" t="s">
         <v>17</v>
@@ -5417,7 +5777,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="C120" t="s">
         <v>17</v>
@@ -5449,7 +5809,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="C121" t="s">
         <v>17</v>
@@ -5481,7 +5841,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="C122" t="s">
         <v>17</v>
@@ -5513,7 +5873,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>119</v>
+        <v>185</v>
       </c>
       <c r="C123" t="s">
         <v>17</v>
@@ -5545,7 +5905,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="C124" t="s">
         <v>17</v>
@@ -5577,7 +5937,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>120</v>
+        <v>187</v>
       </c>
       <c r="C125" t="s">
         <v>17</v>
@@ -5609,7 +5969,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>188</v>
       </c>
       <c r="C126" t="s">
         <v>17</v>
@@ -5641,7 +6001,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>122</v>
+        <v>189</v>
       </c>
       <c r="C127" t="s">
         <v>17</v>
@@ -5673,7 +6033,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="C128" t="s">
         <v>12</v>
@@ -5705,7 +6065,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="C129" t="s">
         <v>17</v>
@@ -5737,7 +6097,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="C130" t="s">
         <v>17</v>
@@ -5769,7 +6129,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="C131" t="s">
         <v>12</v>
@@ -5801,7 +6161,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="C132" t="s">
         <v>8</v>
@@ -5833,7 +6193,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="C133" t="s">
         <v>8</v>
@@ -5865,7 +6225,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="C134" t="s">
         <v>8</v>
@@ -5897,7 +6257,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="C135" t="s">
         <v>8</v>
@@ -5929,7 +6289,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="C136" t="s">
         <v>8</v>
@@ -5961,7 +6321,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="C137" t="s">
         <v>8</v>
@@ -5993,7 +6353,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>130</v>
+        <v>199</v>
       </c>
       <c r="C138" t="s">
         <v>8</v>
@@ -6025,7 +6385,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="C139" t="s">
         <v>8</v>
@@ -6057,7 +6417,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="C140" t="s">
         <v>8</v>
@@ -6089,7 +6449,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="C141" t="s">
         <v>8</v>
@@ -6121,7 +6481,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="C142" t="s">
         <v>12</v>
@@ -6153,7 +6513,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="C143" t="s">
         <v>12</v>
@@ -6185,7 +6545,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="C144" t="s">
         <v>8</v>
@@ -6217,7 +6577,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="C145" t="s">
         <v>8</v>
@@ -6249,7 +6609,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="C146" t="s">
         <v>12</v>
@@ -6281,7 +6641,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -6313,7 +6673,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -6345,7 +6705,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
@@ -6377,7 +6737,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -6409,7 +6769,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -6441,7 +6801,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>140</v>
+        <v>212</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
@@ -6473,7 +6833,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>140</v>
+        <v>213</v>
       </c>
       <c r="C153" t="s">
         <v>17</v>
@@ -6505,7 +6865,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="C154" t="s">
         <v>17</v>
@@ -6537,7 +6897,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>141</v>
+        <v>215</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
@@ -6569,7 +6929,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -6601,7 +6961,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="C157" t="s">
         <v>17</v>
@@ -6633,7 +6993,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="C158" t="s">
         <v>17</v>
@@ -6665,7 +7025,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>144</v>
+        <v>218</v>
       </c>
       <c r="C159" t="s">
         <v>17</v>
@@ -6697,7 +7057,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>145</v>
+        <v>219</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -6729,7 +7089,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
@@ -6761,7 +7121,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
@@ -6793,7 +7153,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>147</v>
+        <v>221</v>
       </c>
       <c r="C163" t="s">
         <v>17</v>
@@ -6825,7 +7185,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -6857,7 +7217,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="C165" t="s">
         <v>12</v>
@@ -6889,7 +7249,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -6921,7 +7281,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="C167" t="s">
         <v>12</v>
@@ -6953,7 +7313,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>151</v>
+        <v>224</v>
       </c>
       <c r="C168" t="s">
         <v>8</v>
@@ -6985,7 +7345,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>152</v>
+        <v>225</v>
       </c>
       <c r="C169" t="s">
         <v>8</v>
@@ -7017,7 +7377,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="C170" t="s">
         <v>8</v>
@@ -7049,7 +7409,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>154</v>
+        <v>227</v>
       </c>
       <c r="C171" t="s">
         <v>8</v>
@@ -7081,7 +7441,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>155</v>
+        <v>228</v>
       </c>
       <c r="C172" t="s">
         <v>8</v>
@@ -7113,7 +7473,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>156</v>
+        <v>229</v>
       </c>
       <c r="C173" t="s">
         <v>8</v>
@@ -7145,7 +7505,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="C174" t="s">
         <v>8</v>
@@ -7177,7 +7537,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="C175" t="s">
         <v>12</v>
@@ -7209,7 +7569,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>158</v>
+        <v>232</v>
       </c>
       <c r="C176" t="s">
         <v>12</v>
@@ -7241,7 +7601,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="C177" t="s">
         <v>10</v>
@@ -7273,7 +7633,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="C178" t="s">
         <v>12</v>
@@ -7305,7 +7665,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="C179" t="s">
         <v>12</v>
@@ -7337,7 +7697,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="C180" t="s">
         <v>12</v>
@@ -7369,7 +7729,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>162</v>
+        <v>237</v>
       </c>
       <c r="C181" t="s">
         <v>12</v>
@@ -7401,7 +7761,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>163</v>
+        <v>238</v>
       </c>
       <c r="C182" t="s">
         <v>8</v>
@@ -7433,7 +7793,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>164</v>
+        <v>239</v>
       </c>
       <c r="C183" t="s">
         <v>8</v>
@@ -7465,7 +7825,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="C184" t="s">
         <v>8</v>
@@ -7497,7 +7857,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="C185" t="s">
         <v>8</v>
@@ -7529,7 +7889,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>167</v>
+        <v>242</v>
       </c>
       <c r="C186" t="s">
         <v>8</v>
@@ -7561,7 +7921,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>167</v>
+        <v>243</v>
       </c>
       <c r="C187" t="s">
         <v>8</v>
@@ -7593,7 +7953,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="C188" t="s">
         <v>8</v>
@@ -7625,7 +7985,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>169</v>
+        <v>245</v>
       </c>
       <c r="C189" t="s">
         <v>12</v>
@@ -7657,7 +8017,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="C190" t="s">
         <v>12</v>
@@ -7689,7 +8049,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="C191" t="s">
         <v>12</v>
@@ -7721,7 +8081,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>171</v>
+        <v>248</v>
       </c>
       <c r="C192" t="s">
         <v>12</v>
@@ -7753,7 +8113,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="C193" t="s">
         <v>8</v>
@@ -7785,7 +8145,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>173</v>
+        <v>250</v>
       </c>
       <c r="C194" t="s">
         <v>8</v>
@@ -7817,7 +8177,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>174</v>
+        <v>251</v>
       </c>
       <c r="C195" t="s">
         <v>8</v>
@@ -7849,7 +8209,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>174</v>
+        <v>252</v>
       </c>
       <c r="C196" t="s">
         <v>8</v>
@@ -7881,7 +8241,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>175</v>
+        <v>253</v>
       </c>
       <c r="C197" t="s">
         <v>12</v>
@@ -7913,7 +8273,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="C198" t="s">
         <v>12</v>
@@ -7945,7 +8305,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>176</v>
+        <v>255</v>
       </c>
       <c r="C199" t="s">
         <v>12</v>
@@ -7977,7 +8337,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="C200" t="s">
         <v>12</v>
@@ -8009,7 +8369,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>177</v>
+        <v>257</v>
       </c>
       <c r="C201" t="s">
         <v>12</v>
@@ -8041,7 +8401,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>178</v>
+        <v>31</v>
       </c>
       <c r="C202" t="s">
         <v>12</v>
@@ -8073,7 +8433,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>179</v>
+        <v>258</v>
       </c>
       <c r="C203" t="s">
         <v>12</v>
@@ -8105,7 +8465,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C204" t="s">
         <v>12</v>
@@ -8137,7 +8497,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>181</v>
+        <v>260</v>
       </c>
       <c r="C205" t="s">
         <v>10</v>
@@ -8169,7 +8529,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>182</v>
+        <v>261</v>
       </c>
       <c r="C206" t="s">
         <v>12</v>
@@ -8201,7 +8561,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>183</v>
+        <v>262</v>
       </c>
       <c r="C207" t="s">
         <v>12</v>
@@ -8233,7 +8593,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>184</v>
+        <v>263</v>
       </c>
       <c r="C208" t="s">
         <v>12</v>
@@ -8265,7 +8625,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>184</v>
+        <v>264</v>
       </c>
       <c r="C209" t="s">
         <v>12</v>
@@ -8297,7 +8657,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="C210" t="s">
         <v>8</v>
@@ -8329,7 +8689,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>186</v>
+        <v>266</v>
       </c>
       <c r="C211" t="s">
         <v>8</v>
@@ -8361,7 +8721,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>187</v>
+        <v>267</v>
       </c>
       <c r="C212" t="s">
         <v>8</v>
@@ -8393,7 +8753,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>188</v>
+        <v>268</v>
       </c>
       <c r="C213" t="s">
         <v>8</v>
@@ -8425,7 +8785,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="C214" t="s">
         <v>8</v>
@@ -8457,7 +8817,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>189</v>
+        <v>270</v>
       </c>
       <c r="C215" t="s">
         <v>8</v>
@@ -8489,7 +8849,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>190</v>
+        <v>271</v>
       </c>
       <c r="C216" t="s">
         <v>8</v>
@@ -8521,7 +8881,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>191</v>
+        <v>272</v>
       </c>
       <c r="C217" t="s">
         <v>12</v>
@@ -8553,7 +8913,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>192</v>
+        <v>273</v>
       </c>
       <c r="C218" t="s">
         <v>12</v>
@@ -8585,7 +8945,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>193</v>
+        <v>274</v>
       </c>
       <c r="C219" t="s">
         <v>12</v>
@@ -8617,7 +8977,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>193</v>
+        <v>275</v>
       </c>
       <c r="C220" t="s">
         <v>12</v>
@@ -8649,7 +9009,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="C221" t="s">
         <v>8</v>
@@ -8681,7 +9041,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>195</v>
+        <v>277</v>
       </c>
       <c r="C222" t="s">
         <v>8</v>
@@ -8713,7 +9073,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>196</v>
+        <v>278</v>
       </c>
       <c r="C223" t="s">
         <v>8</v>
@@ -8745,7 +9105,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>196</v>
+        <v>279</v>
       </c>
       <c r="C224" t="s">
         <v>8</v>
@@ -8777,7 +9137,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>197</v>
+        <v>280</v>
       </c>
       <c r="C225" t="s">
         <v>12</v>
@@ -8809,7 +9169,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>198</v>
+        <v>281</v>
       </c>
       <c r="C226" t="s">
         <v>12</v>
@@ -8841,7 +9201,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>198</v>
+        <v>282</v>
       </c>
       <c r="C227" t="s">
         <v>12</v>
@@ -8873,7 +9233,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>199</v>
+        <v>283</v>
       </c>
       <c r="C228" t="s">
         <v>12</v>
@@ -8905,7 +9265,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="C229" t="s">
         <v>12</v>
@@ -8937,7 +9297,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="C230" t="s">
         <v>12</v>
@@ -8969,7 +9329,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>201</v>
+        <v>285</v>
       </c>
       <c r="C231" t="s">
         <v>12</v>
@@ -9001,7 +9361,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="C232" t="s">
         <v>10</v>
@@ -9033,7 +9393,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="C233" t="s">
         <v>12</v>
@@ -9065,7 +9425,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>204</v>
+        <v>288</v>
       </c>
       <c r="C234" t="s">
         <v>12</v>
@@ -9097,7 +9457,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="C235" t="s">
         <v>12</v>
@@ -9129,7 +9489,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="C236" t="s">
         <v>12</v>
@@ -9161,7 +9521,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>206</v>
+        <v>291</v>
       </c>
       <c r="C237" t="s">
         <v>17</v>
@@ -9193,7 +9553,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="C238" t="s">
         <v>12</v>
@@ -9225,7 +9585,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>208</v>
+        <v>293</v>
       </c>
       <c r="C239" t="s">
         <v>12</v>
@@ -9257,7 +9617,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="C240" t="s">
         <v>12</v>
@@ -9289,7 +9649,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>209</v>
+        <v>295</v>
       </c>
       <c r="C241" t="s">
         <v>12</v>
@@ -9321,7 +9681,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>210</v>
+        <v>296</v>
       </c>
       <c r="C242" t="s">
         <v>17</v>
@@ -9353,7 +9713,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>211</v>
+        <v>297</v>
       </c>
       <c r="C243" t="s">
         <v>17</v>
@@ -9385,7 +9745,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>212</v>
+        <v>298</v>
       </c>
       <c r="C244" t="s">
         <v>17</v>
@@ -9417,7 +9777,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="C245" t="s">
         <v>17</v>
@@ -9449,7 +9809,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="C246" t="s">
         <v>12</v>
@@ -9481,7 +9841,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
       <c r="C247" t="s">
         <v>17</v>
@@ -9513,7 +9873,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>214</v>
+        <v>302</v>
       </c>
       <c r="C248" t="s">
         <v>12</v>
@@ -9545,7 +9905,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>215</v>
+        <v>303</v>
       </c>
       <c r="C249" t="s">
         <v>12</v>
@@ -9577,7 +9937,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>215</v>
+        <v>304</v>
       </c>
       <c r="C250" t="s">
         <v>12</v>
@@ -9609,7 +9969,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>216</v>
+        <v>33</v>
       </c>
       <c r="C251" t="s">
         <v>12</v>
@@ -9641,7 +10001,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>217</v>
+        <v>305</v>
       </c>
       <c r="C252" t="s">
         <v>8</v>
@@ -9673,7 +10033,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>218</v>
+        <v>306</v>
       </c>
       <c r="C253" t="s">
         <v>12</v>
@@ -9705,7 +10065,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>219</v>
+        <v>307</v>
       </c>
       <c r="C254" t="s">
         <v>12</v>
@@ -9737,7 +10097,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="C255" t="s">
         <v>12</v>
@@ -9769,7 +10129,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>220</v>
+        <v>309</v>
       </c>
       <c r="C256" t="s">
         <v>12</v>
@@ -9801,7 +10161,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>221</v>
+        <v>310</v>
       </c>
       <c r="C257" t="s">
         <v>8</v>
@@ -9833,7 +10193,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>222</v>
+        <v>311</v>
       </c>
       <c r="C258" t="s">
         <v>8</v>
@@ -9865,7 +10225,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="C259" t="s">
         <v>8</v>
@@ -9897,7 +10257,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="C260" t="s">
         <v>8</v>
@@ -9929,7 +10289,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>224</v>
+        <v>314</v>
       </c>
       <c r="C261" t="s">
         <v>12</v>
@@ -9961,7 +10321,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="C262" t="s">
         <v>12</v>
@@ -9993,7 +10353,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>225</v>
+        <v>316</v>
       </c>
       <c r="C263" t="s">
         <v>12</v>
@@ -10025,7 +10385,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>226</v>
+        <v>317</v>
       </c>
       <c r="C264" t="s">
         <v>12</v>
@@ -10057,7 +10417,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>226</v>
+        <v>318</v>
       </c>
       <c r="C265" t="s">
         <v>12</v>
@@ -10089,7 +10449,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>227</v>
+        <v>34</v>
       </c>
       <c r="C266" t="s">
         <v>12</v>
@@ -10121,7 +10481,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>228</v>
+        <v>319</v>
       </c>
       <c r="C267" t="s">
         <v>17</v>
@@ -10153,7 +10513,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>229</v>
+        <v>320</v>
       </c>
       <c r="C268" t="s">
         <v>17</v>
@@ -10185,7 +10545,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>230</v>
+        <v>321</v>
       </c>
       <c r="C269" t="s">
         <v>17</v>
@@ -10217,7 +10577,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>230</v>
+        <v>322</v>
       </c>
       <c r="C270" t="s">
         <v>17</v>
@@ -10249,7 +10609,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>231</v>
+        <v>323</v>
       </c>
       <c r="C271" t="s">
         <v>12</v>
@@ -10281,7 +10641,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>232</v>
+        <v>324</v>
       </c>
       <c r="C272" t="s">
         <v>12</v>
@@ -10313,7 +10673,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="C273" t="s">
         <v>12</v>
@@ -10345,7 +10705,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>233</v>
+        <v>326</v>
       </c>
       <c r="C274" t="s">
         <v>12</v>
@@ -10377,7 +10737,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>233</v>
+        <v>327</v>
       </c>
       <c r="C275" t="s">
         <v>12</v>
@@ -10409,7 +10769,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>234</v>
+        <v>35</v>
       </c>
       <c r="C276" t="s">
         <v>12</v>
@@ -10441,7 +10801,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>235</v>
+        <v>328</v>
       </c>
       <c r="C277" t="s">
         <v>17</v>
@@ -10473,7 +10833,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>236</v>
+        <v>329</v>
       </c>
       <c r="C278" t="s">
         <v>17</v>
@@ -10505,7 +10865,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>236</v>
+        <v>330</v>
       </c>
       <c r="C279" t="s">
         <v>17</v>
@@ -10537,7 +10897,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>237</v>
+        <v>331</v>
       </c>
       <c r="C280" t="s">
         <v>17</v>
@@ -10569,7 +10929,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>237</v>
+        <v>332</v>
       </c>
       <c r="C281" t="s">
         <v>17</v>
@@ -10601,7 +10961,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>238</v>
+        <v>36</v>
       </c>
       <c r="C282" t="s">
         <v>17</v>
@@ -10633,7 +10993,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>239</v>
+        <v>333</v>
       </c>
       <c r="C283" t="s">
         <v>12</v>
@@ -10665,7 +11025,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>239</v>
+        <v>334</v>
       </c>
       <c r="C284" t="s">
         <v>12</v>
@@ -10697,7 +11057,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>240</v>
+        <v>37</v>
       </c>
       <c r="C285" t="s">
         <v>12</v>
@@ -10729,7 +11089,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>241</v>
+        <v>38</v>
       </c>
       <c r="C286" t="s">
         <v>12</v>
@@ -10761,7 +11121,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>242</v>
+        <v>335</v>
       </c>
       <c r="C287" t="s">
         <v>12</v>
@@ -10793,7 +11153,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>243</v>
+        <v>336</v>
       </c>
       <c r="C288" t="s">
         <v>12</v>
@@ -10825,7 +11185,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="C289" t="s">
         <v>10</v>
@@ -10857,7 +11217,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>245</v>
+        <v>338</v>
       </c>
       <c r="C290" t="s">
         <v>12</v>
@@ -10889,7 +11249,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="C291" t="s">
         <v>12</v>
@@ -10921,7 +11281,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>247</v>
+        <v>340</v>
       </c>
       <c r="C292" t="s">
         <v>12</v>
@@ -10953,7 +11313,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>247</v>
+        <v>341</v>
       </c>
       <c r="C293" t="s">
         <v>12</v>
@@ -10985,7 +11345,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>248</v>
+        <v>342</v>
       </c>
       <c r="C294" t="s">
         <v>8</v>
@@ -11017,7 +11377,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>249</v>
+        <v>343</v>
       </c>
       <c r="C295" t="s">
         <v>8</v>
@@ -11049,7 +11409,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>250</v>
+        <v>344</v>
       </c>
       <c r="C296" t="s">
         <v>8</v>
@@ -11081,7 +11441,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>251</v>
+        <v>345</v>
       </c>
       <c r="C297" t="s">
         <v>8</v>
@@ -11113,7 +11473,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>252</v>
+        <v>346</v>
       </c>
       <c r="C298" t="s">
         <v>8</v>
@@ -11145,7 +11505,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>252</v>
+        <v>347</v>
       </c>
       <c r="C299" t="s">
         <v>8</v>
@@ -11177,7 +11537,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>253</v>
+        <v>348</v>
       </c>
       <c r="C300" t="s">
         <v>8</v>
@@ -11209,7 +11569,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>254</v>
+        <v>349</v>
       </c>
       <c r="C301" t="s">
         <v>8</v>
@@ -11241,7 +11601,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>255</v>
+        <v>350</v>
       </c>
       <c r="C302" t="s">
         <v>8</v>
@@ -11273,7 +11633,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>256</v>
+        <v>351</v>
       </c>
       <c r="C303" t="s">
         <v>8</v>
@@ -11305,7 +11665,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>256</v>
+        <v>352</v>
       </c>
       <c r="C304" t="s">
         <v>8</v>
@@ -11337,7 +11697,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>257</v>
+        <v>353</v>
       </c>
       <c r="C305" t="s">
         <v>8</v>
@@ -11369,7 +11729,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>258</v>
+        <v>354</v>
       </c>
       <c r="C306" t="s">
         <v>8</v>
@@ -11401,7 +11761,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>259</v>
+        <v>355</v>
       </c>
       <c r="C307" t="s">
         <v>8</v>
@@ -11433,7 +11793,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>259</v>
+        <v>356</v>
       </c>
       <c r="C308" t="s">
         <v>8</v>
@@ -11465,7 +11825,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="C309" t="s">
         <v>8</v>
@@ -11497,7 +11857,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>261</v>
+        <v>358</v>
       </c>
       <c r="C310" t="s">
         <v>12</v>
@@ -11529,7 +11889,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>261</v>
+        <v>359</v>
       </c>
       <c r="C311" t="s">
         <v>12</v>
@@ -11561,7 +11921,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>262</v>
+        <v>360</v>
       </c>
       <c r="C312" t="s">
         <v>8</v>
@@ -11593,7 +11953,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>262</v>
+        <v>361</v>
       </c>
       <c r="C313" t="s">
         <v>8</v>
@@ -11625,7 +11985,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>263</v>
+        <v>39</v>
       </c>
       <c r="C314" t="s">
         <v>12</v>
@@ -11657,7 +12017,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>264</v>
+        <v>362</v>
       </c>
       <c r="C315" t="s">
         <v>10</v>
@@ -11689,7 +12049,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>265</v>
+        <v>363</v>
       </c>
       <c r="C316" t="s">
         <v>10</v>
@@ -11721,7 +12081,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>266</v>
+        <v>364</v>
       </c>
       <c r="C317" t="s">
         <v>12</v>
@@ -11753,7 +12113,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>267</v>
+        <v>365</v>
       </c>
       <c r="C318" t="s">
         <v>10</v>
@@ -11785,7 +12145,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>268</v>
+        <v>366</v>
       </c>
       <c r="C319" t="s">
         <v>12</v>
@@ -11817,7 +12177,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>268</v>
+        <v>367</v>
       </c>
       <c r="C320" t="s">
         <v>12</v>
@@ -11849,7 +12209,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>269</v>
+        <v>368</v>
       </c>
       <c r="C321" t="s">
         <v>10</v>
@@ -11881,7 +12241,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>270</v>
+        <v>369</v>
       </c>
       <c r="C322" t="s">
         <v>12</v>
@@ -11913,7 +12273,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>271</v>
+        <v>370</v>
       </c>
       <c r="C323" t="s">
         <v>12</v>
@@ -11945,7 +12305,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>272</v>
+        <v>371</v>
       </c>
       <c r="C324" t="s">
         <v>12</v>
@@ -11977,7 +12337,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>272</v>
+        <v>372</v>
       </c>
       <c r="C325" t="s">
         <v>12</v>
@@ -12009,7 +12369,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>273</v>
+        <v>373</v>
       </c>
       <c r="C326" t="s">
         <v>11</v>
@@ -12041,7 +12401,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>274</v>
+        <v>374</v>
       </c>
       <c r="C327" t="s">
         <v>10</v>
@@ -12073,7 +12433,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>275</v>
+        <v>375</v>
       </c>
       <c r="C328" t="s">
         <v>11</v>
@@ -12105,7 +12465,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>275</v>
+        <v>376</v>
       </c>
       <c r="C329" t="s">
         <v>11</v>
@@ -12137,7 +12497,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>276</v>
+        <v>377</v>
       </c>
       <c r="C330" t="s">
         <v>12</v>
@@ -12169,7 +12529,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="C331" t="s">
         <v>12</v>
@@ -12201,7 +12561,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>277</v>
+        <v>379</v>
       </c>
       <c r="C332" t="s">
         <v>12</v>
@@ -12233,7 +12593,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>278</v>
+        <v>380</v>
       </c>
       <c r="C333" t="s">
         <v>12</v>
@@ -12265,7 +12625,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>278</v>
+        <v>381</v>
       </c>
       <c r="C334" t="s">
         <v>12</v>
@@ -12297,7 +12657,7 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="C335" t="s">
         <v>12</v>
@@ -12329,7 +12689,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>280</v>
+        <v>382</v>
       </c>
       <c r="C336" t="s">
         <v>8</v>
@@ -12361,7 +12721,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>281</v>
+        <v>383</v>
       </c>
       <c r="C337" t="s">
         <v>8</v>
@@ -12393,7 +12753,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>282</v>
+        <v>384</v>
       </c>
       <c r="C338" t="s">
         <v>8</v>
@@ -12425,7 +12785,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>283</v>
+        <v>385</v>
       </c>
       <c r="C339" t="s">
         <v>8</v>
@@ -12457,7 +12817,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>283</v>
+        <v>386</v>
       </c>
       <c r="C340" t="s">
         <v>8</v>
@@ -12489,7 +12849,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>284</v>
+        <v>387</v>
       </c>
       <c r="C341" t="s">
         <v>8</v>
@@ -12521,7 +12881,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>285</v>
+        <v>388</v>
       </c>
       <c r="C342" t="s">
         <v>8</v>
@@ -12553,7 +12913,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>286</v>
+        <v>389</v>
       </c>
       <c r="C343" t="s">
         <v>8</v>
@@ -12585,7 +12945,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>286</v>
+        <v>390</v>
       </c>
       <c r="C344" t="s">
         <v>8</v>
@@ -12617,7 +12977,7 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>287</v>
+        <v>391</v>
       </c>
       <c r="C345" t="s">
         <v>8</v>
@@ -12649,7 +13009,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>288</v>
+        <v>392</v>
       </c>
       <c r="C346" t="s">
         <v>12</v>
@@ -12681,7 +13041,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>288</v>
+        <v>393</v>
       </c>
       <c r="C347" t="s">
         <v>12</v>
@@ -12713,7 +13073,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>289</v>
+        <v>394</v>
       </c>
       <c r="C348" t="s">
         <v>8</v>
@@ -12745,7 +13105,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>289</v>
+        <v>395</v>
       </c>
       <c r="C349" t="s">
         <v>8</v>
@@ -12777,7 +13137,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>290</v>
+        <v>41</v>
       </c>
       <c r="C350" t="s">
         <v>12</v>
@@ -12809,7 +13169,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>291</v>
+        <v>396</v>
       </c>
       <c r="C351" t="s">
         <v>8</v>
@@ -12841,7 +13201,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>292</v>
+        <v>397</v>
       </c>
       <c r="C352" t="s">
         <v>8</v>
@@ -12873,7 +13233,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>293</v>
+        <v>398</v>
       </c>
       <c r="C353" t="s">
         <v>8</v>
@@ -12905,7 +13265,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>293</v>
+        <v>399</v>
       </c>
       <c r="C354" t="s">
         <v>8</v>
@@ -12937,7 +13297,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>294</v>
+        <v>400</v>
       </c>
       <c r="C355" t="s">
         <v>12</v>
@@ -12969,7 +13329,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>295</v>
+        <v>401</v>
       </c>
       <c r="C356" t="s">
         <v>12</v>
@@ -13001,7 +13361,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>295</v>
+        <v>402</v>
       </c>
       <c r="C357" t="s">
         <v>12</v>
@@ -13033,7 +13393,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>296</v>
+        <v>403</v>
       </c>
       <c r="C358" t="s">
         <v>12</v>
@@ -13065,7 +13425,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>296</v>
+        <v>404</v>
       </c>
       <c r="C359" t="s">
         <v>12</v>
@@ -13097,7 +13457,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>297</v>
+        <v>42</v>
       </c>
       <c r="C360" t="s">
         <v>12</v>
@@ -13129,7 +13489,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>298</v>
+        <v>405</v>
       </c>
       <c r="C361" t="s">
         <v>8</v>
@@ -13161,7 +13521,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>299</v>
+        <v>406</v>
       </c>
       <c r="C362" t="s">
         <v>8</v>
@@ -13193,7 +13553,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>299</v>
+        <v>407</v>
       </c>
       <c r="C363" t="s">
         <v>8</v>
@@ -13225,7 +13585,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>300</v>
+        <v>408</v>
       </c>
       <c r="C364" t="s">
         <v>8</v>
@@ -13257,7 +13617,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>300</v>
+        <v>409</v>
       </c>
       <c r="C365" t="s">
         <v>8</v>
@@ -13289,7 +13649,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>301</v>
+        <v>43</v>
       </c>
       <c r="C366" t="s">
         <v>8</v>
@@ -13321,7 +13681,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>302</v>
+        <v>410</v>
       </c>
       <c r="C367" t="s">
         <v>12</v>
@@ -13353,7 +13713,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>302</v>
+        <v>411</v>
       </c>
       <c r="C368" t="s">
         <v>12</v>
@@ -13385,7 +13745,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>303</v>
+        <v>44</v>
       </c>
       <c r="C369" t="s">
         <v>12</v>
@@ -13417,7 +13777,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>304</v>
+        <v>45</v>
       </c>
       <c r="C370" t="s">
         <v>12</v>
@@ -13449,7 +13809,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>305</v>
+        <v>412</v>
       </c>
       <c r="C371" t="s">
         <v>10</v>
@@ -13481,7 +13841,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>306</v>
+        <v>413</v>
       </c>
       <c r="C372" t="s">
         <v>10</v>
@@ -13513,7 +13873,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>307</v>
+        <v>414</v>
       </c>
       <c r="C373" t="s">
         <v>12</v>
@@ -13545,7 +13905,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>308</v>
+        <v>415</v>
       </c>
       <c r="C374" t="s">
         <v>10</v>
@@ -13577,7 +13937,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>309</v>
+        <v>416</v>
       </c>
       <c r="C375" t="s">
         <v>12</v>
@@ -13609,7 +13969,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>309</v>
+        <v>417</v>
       </c>
       <c r="C376" t="s">
         <v>12</v>
@@ -13641,7 +14001,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>310</v>
+        <v>418</v>
       </c>
       <c r="C377" t="s">
         <v>10</v>
@@ -13673,7 +14033,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>311</v>
+        <v>419</v>
       </c>
       <c r="C378" t="s">
         <v>12</v>
@@ -13705,7 +14065,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>312</v>
+        <v>420</v>
       </c>
       <c r="C379" t="s">
         <v>12</v>
@@ -13737,7 +14097,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>313</v>
+        <v>421</v>
       </c>
       <c r="C380" t="s">
         <v>12</v>
@@ -13769,7 +14129,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>313</v>
+        <v>422</v>
       </c>
       <c r="C381" t="s">
         <v>12</v>
@@ -13801,7 +14161,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>314</v>
+        <v>423</v>
       </c>
       <c r="C382" t="s">
         <v>17</v>
@@ -13833,7 +14193,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>315</v>
+        <v>424</v>
       </c>
       <c r="C383" t="s">
         <v>10</v>
@@ -13865,7 +14225,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>316</v>
+        <v>425</v>
       </c>
       <c r="C384" t="s">
         <v>17</v>
@@ -13897,7 +14257,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>316</v>
+        <v>426</v>
       </c>
       <c r="C385" t="s">
         <v>17</v>
@@ -13929,7 +14289,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>317</v>
+        <v>427</v>
       </c>
       <c r="C386" t="s">
         <v>12</v>
@@ -13961,7 +14321,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>318</v>
+        <v>428</v>
       </c>
       <c r="C387" t="s">
         <v>12</v>
@@ -13993,7 +14353,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>318</v>
+        <v>429</v>
       </c>
       <c r="C388" t="s">
         <v>12</v>
@@ -14025,7 +14385,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="C389" t="s">
         <v>12</v>
@@ -14057,7 +14417,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>319</v>
+        <v>431</v>
       </c>
       <c r="C390" t="s">
         <v>12</v>
@@ -14089,7 +14449,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>320</v>
+        <v>46</v>
       </c>
       <c r="C391" t="s">
         <v>12</v>
@@ -14121,7 +14481,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>321</v>
+        <v>432</v>
       </c>
       <c r="C392" t="s">
         <v>8</v>
@@ -14153,7 +14513,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>322</v>
+        <v>433</v>
       </c>
       <c r="C393" t="s">
         <v>8</v>
@@ -14185,7 +14545,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>323</v>
+        <v>434</v>
       </c>
       <c r="C394" t="s">
         <v>8</v>
@@ -14217,7 +14577,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>324</v>
+        <v>435</v>
       </c>
       <c r="C395" t="s">
         <v>8</v>
@@ -14249,7 +14609,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>324</v>
+        <v>436</v>
       </c>
       <c r="C396" t="s">
         <v>8</v>
@@ -14281,7 +14641,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="C397" t="s">
         <v>8</v>
@@ -14313,7 +14673,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
       <c r="C398" t="s">
         <v>8</v>
@@ -14345,7 +14705,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>327</v>
+        <v>439</v>
       </c>
       <c r="C399" t="s">
         <v>8</v>
@@ -14377,7 +14737,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>327</v>
+        <v>440</v>
       </c>
       <c r="C400" t="s">
         <v>8</v>
@@ -14409,7 +14769,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>328</v>
+        <v>441</v>
       </c>
       <c r="C401" t="s">
         <v>8</v>
@@ -14441,7 +14801,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>329</v>
+        <v>442</v>
       </c>
       <c r="C402" t="s">
         <v>12</v>
@@ -14473,7 +14833,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>329</v>
+        <v>443</v>
       </c>
       <c r="C403" t="s">
         <v>12</v>
@@ -14505,7 +14865,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>330</v>
+        <v>444</v>
       </c>
       <c r="C404" t="s">
         <v>8</v>
@@ -14537,7 +14897,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="C405" t="s">
         <v>8</v>
@@ -14569,7 +14929,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>331</v>
+        <v>47</v>
       </c>
       <c r="C406" t="s">
         <v>12</v>
@@ -14601,7 +14961,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>332</v>
+        <v>446</v>
       </c>
       <c r="C407" t="s">
         <v>8</v>
@@ -14633,7 +14993,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>333</v>
+        <v>447</v>
       </c>
       <c r="C408" t="s">
         <v>8</v>
@@ -14665,7 +15025,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>334</v>
+        <v>448</v>
       </c>
       <c r="C409" t="s">
         <v>8</v>
@@ -14697,7 +15057,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>334</v>
+        <v>449</v>
       </c>
       <c r="C410" t="s">
         <v>8</v>
@@ -14729,7 +15089,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>335</v>
+        <v>450</v>
       </c>
       <c r="C411" t="s">
         <v>12</v>
@@ -14761,7 +15121,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>336</v>
+        <v>451</v>
       </c>
       <c r="C412" t="s">
         <v>12</v>
@@ -14793,7 +15153,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>336</v>
+        <v>452</v>
       </c>
       <c r="C413" t="s">
         <v>12</v>
@@ -14825,7 +15185,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>337</v>
+        <v>453</v>
       </c>
       <c r="C414" t="s">
         <v>12</v>
@@ -14857,7 +15217,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>337</v>
+        <v>454</v>
       </c>
       <c r="C415" t="s">
         <v>12</v>
@@ -14889,7 +15249,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>338</v>
+        <v>48</v>
       </c>
       <c r="C416" t="s">
         <v>12</v>
@@ -14921,7 +15281,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>339</v>
+        <v>455</v>
       </c>
       <c r="C417" t="s">
         <v>8</v>
@@ -14953,7 +15313,7 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
       <c r="C418" t="s">
         <v>8</v>
@@ -14985,7 +15345,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>340</v>
+        <v>457</v>
       </c>
       <c r="C419" t="s">
         <v>8</v>
@@ -15017,7 +15377,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>341</v>
+        <v>458</v>
       </c>
       <c r="C420" t="s">
         <v>8</v>
@@ -15049,7 +15409,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>341</v>
+        <v>459</v>
       </c>
       <c r="C421" t="s">
         <v>8</v>
@@ -15081,7 +15441,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>342</v>
+        <v>49</v>
       </c>
       <c r="C422" t="s">
         <v>8</v>
@@ -15113,7 +15473,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>343</v>
+        <v>460</v>
       </c>
       <c r="C423" t="s">
         <v>12</v>
@@ -15145,7 +15505,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>343</v>
+        <v>461</v>
       </c>
       <c r="C424" t="s">
         <v>12</v>
@@ -15177,7 +15537,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>344</v>
+        <v>50</v>
       </c>
       <c r="C425" t="s">
         <v>12</v>
@@ -15209,7 +15569,7 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>345</v>
+        <v>51</v>
       </c>
       <c r="C426" t="s">
         <v>12</v>
@@ -15241,7 +15601,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="C427" t="s">
         <v>10</v>
@@ -15273,7 +15633,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>347</v>
+        <v>463</v>
       </c>
       <c r="C428" t="s">
         <v>12</v>
@@ -15305,7 +15665,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>348</v>
+        <v>464</v>
       </c>
       <c r="C429" t="s">
         <v>12</v>
@@ -15337,7 +15697,7 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>349</v>
+        <v>465</v>
       </c>
       <c r="C430" t="s">
         <v>12</v>
@@ -15369,7 +15729,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>349</v>
+        <v>466</v>
       </c>
       <c r="C431" t="s">
         <v>12</v>
@@ -15401,7 +15761,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>350</v>
+        <v>467</v>
       </c>
       <c r="C432" t="s">
         <v>17</v>
@@ -15433,7 +15793,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>351</v>
+        <v>468</v>
       </c>
       <c r="C433" t="s">
         <v>10</v>
@@ -15465,7 +15825,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>352</v>
+        <v>469</v>
       </c>
       <c r="C434" t="s">
         <v>17</v>
@@ -15497,7 +15857,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="C435" t="s">
         <v>17</v>
@@ -15529,7 +15889,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>353</v>
+        <v>471</v>
       </c>
       <c r="C436" t="s">
         <v>12</v>
@@ -15561,7 +15921,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>354</v>
+        <v>472</v>
       </c>
       <c r="C437" t="s">
         <v>12</v>
@@ -15593,7 +15953,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>354</v>
+        <v>473</v>
       </c>
       <c r="C438" t="s">
         <v>12</v>
@@ -15625,7 +15985,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>355</v>
+        <v>474</v>
       </c>
       <c r="C439" t="s">
         <v>12</v>
@@ -15657,7 +16017,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>355</v>
+        <v>475</v>
       </c>
       <c r="C440" t="s">
         <v>12</v>
@@ -15689,7 +16049,7 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>356</v>
+        <v>52</v>
       </c>
       <c r="C441" t="s">
         <v>12</v>
@@ -15721,7 +16081,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>357</v>
+        <v>476</v>
       </c>
       <c r="C442" t="s">
         <v>17</v>
@@ -15753,7 +16113,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>358</v>
+        <v>477</v>
       </c>
       <c r="C443" t="s">
         <v>17</v>
@@ -15785,7 +16145,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="s">
-        <v>359</v>
+        <v>478</v>
       </c>
       <c r="C444" t="s">
         <v>17</v>
@@ -15817,7 +16177,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>359</v>
+        <v>479</v>
       </c>
       <c r="C445" t="s">
         <v>17</v>
@@ -15849,7 +16209,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="C446" t="s">
         <v>12</v>
@@ -15881,7 +16241,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>361</v>
+        <v>481</v>
       </c>
       <c r="C447" t="s">
         <v>17</v>
@@ -15913,7 +16273,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>361</v>
+        <v>482</v>
       </c>
       <c r="C448" t="s">
         <v>12</v>
@@ -15945,7 +16305,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>362</v>
+        <v>483</v>
       </c>
       <c r="C449" t="s">
         <v>12</v>
@@ -15977,7 +16337,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>362</v>
+        <v>484</v>
       </c>
       <c r="C450" t="s">
         <v>12</v>
@@ -16009,7 +16369,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>363</v>
+        <v>53</v>
       </c>
       <c r="C451" t="s">
         <v>12</v>
@@ -16041,7 +16401,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>364</v>
+        <v>485</v>
       </c>
       <c r="C452" t="s">
         <v>17</v>
@@ -16073,7 +16433,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>365</v>
+        <v>486</v>
       </c>
       <c r="C453" t="s">
         <v>17</v>
@@ -16105,7 +16465,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>365</v>
+        <v>487</v>
       </c>
       <c r="C454" t="s">
         <v>17</v>
@@ -16137,7 +16497,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>366</v>
+        <v>488</v>
       </c>
       <c r="C455" t="s">
         <v>17</v>
@@ -16169,7 +16529,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>366</v>
+        <v>489</v>
       </c>
       <c r="C456" t="s">
         <v>17</v>
@@ -16201,7 +16561,7 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>367</v>
+        <v>54</v>
       </c>
       <c r="C457" t="s">
         <v>17</v>
@@ -16233,7 +16593,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="s">
-        <v>368</v>
+        <v>490</v>
       </c>
       <c r="C458" t="s">
         <v>17</v>
@@ -16265,7 +16625,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>368</v>
+        <v>491</v>
       </c>
       <c r="C459" t="s">
         <v>12</v>
@@ -16297,7 +16657,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>369</v>
+        <v>55</v>
       </c>
       <c r="C460" t="s">
         <v>12</v>
@@ -16329,7 +16689,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>370</v>
+        <v>56</v>
       </c>
       <c r="C461" t="s">
         <v>12</v>
@@ -16361,7 +16721,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
-        <v>371</v>
+        <v>492</v>
       </c>
       <c r="C462" t="s">
         <v>8</v>
@@ -16393,7 +16753,7 @@
         <v>462</v>
       </c>
       <c r="B463" t="s">
-        <v>372</v>
+        <v>493</v>
       </c>
       <c r="C463" t="s">
         <v>8</v>
@@ -16425,7 +16785,7 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>373</v>
+        <v>494</v>
       </c>
       <c r="C464" t="s">
         <v>8</v>
@@ -16457,7 +16817,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>373</v>
+        <v>495</v>
       </c>
       <c r="C465" t="s">
         <v>8</v>
@@ -16489,7 +16849,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>374</v>
+        <v>496</v>
       </c>
       <c r="C466" t="s">
         <v>12</v>
@@ -16521,7 +16881,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="s">
-        <v>375</v>
+        <v>497</v>
       </c>
       <c r="C467" t="s">
         <v>12</v>
@@ -16553,7 +16913,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="s">
-        <v>375</v>
+        <v>498</v>
       </c>
       <c r="C468" t="s">
         <v>12</v>
@@ -16585,7 +16945,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>376</v>
+        <v>499</v>
       </c>
       <c r="C469" t="s">
         <v>12</v>
@@ -16617,7 +16977,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="s">
-        <v>376</v>
+        <v>500</v>
       </c>
       <c r="C470" t="s">
         <v>12</v>
@@ -16649,7 +17009,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
-        <v>377</v>
+        <v>57</v>
       </c>
       <c r="C471" t="s">
         <v>12</v>
@@ -16681,7 +17041,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="s">
-        <v>378</v>
+        <v>501</v>
       </c>
       <c r="C472" t="s">
         <v>8</v>
@@ -16713,7 +17073,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="s">
-        <v>379</v>
+        <v>502</v>
       </c>
       <c r="C473" t="s">
         <v>8</v>
@@ -16745,7 +17105,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="s">
-        <v>379</v>
+        <v>503</v>
       </c>
       <c r="C474" t="s">
         <v>8</v>
@@ -16777,7 +17137,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="s">
-        <v>380</v>
+        <v>504</v>
       </c>
       <c r="C475" t="s">
         <v>8</v>
@@ -16809,7 +17169,7 @@
         <v>475</v>
       </c>
       <c r="B476" t="s">
-        <v>380</v>
+        <v>505</v>
       </c>
       <c r="C476" t="s">
         <v>8</v>
@@ -16841,7 +17201,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="s">
-        <v>381</v>
+        <v>58</v>
       </c>
       <c r="C477" t="s">
         <v>8</v>
@@ -16873,7 +17233,7 @@
         <v>477</v>
       </c>
       <c r="B478" t="s">
-        <v>382</v>
+        <v>506</v>
       </c>
       <c r="C478" t="s">
         <v>12</v>
@@ -16905,7 +17265,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="s">
-        <v>382</v>
+        <v>507</v>
       </c>
       <c r="C479" t="s">
         <v>12</v>
@@ -16937,7 +17297,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="s">
-        <v>383</v>
+        <v>59</v>
       </c>
       <c r="C480" t="s">
         <v>12</v>
@@ -16969,7 +17329,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="s">
-        <v>384</v>
+        <v>60</v>
       </c>
       <c r="C481" t="s">
         <v>12</v>
@@ -17001,7 +17361,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="s">
-        <v>385</v>
+        <v>508</v>
       </c>
       <c r="C482" t="s">
         <v>17</v>
@@ -17033,7 +17393,7 @@
         <v>482</v>
       </c>
       <c r="B483" t="s">
-        <v>386</v>
+        <v>509</v>
       </c>
       <c r="C483" t="s">
         <v>17</v>
@@ -17065,7 +17425,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="s">
-        <v>386</v>
+        <v>510</v>
       </c>
       <c r="C484" t="s">
         <v>17</v>
@@ -17097,7 +17457,7 @@
         <v>484</v>
       </c>
       <c r="B485" t="s">
-        <v>387</v>
+        <v>511</v>
       </c>
       <c r="C485" t="s">
         <v>17</v>
@@ -17129,7 +17489,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="s">
-        <v>387</v>
+        <v>512</v>
       </c>
       <c r="C486" t="s">
         <v>17</v>
@@ -17161,7 +17521,7 @@
         <v>486</v>
       </c>
       <c r="B487" t="s">
-        <v>388</v>
+        <v>61</v>
       </c>
       <c r="C487" t="s">
         <v>17</v>
@@ -17193,7 +17553,7 @@
         <v>487</v>
       </c>
       <c r="B488" t="s">
-        <v>389</v>
+        <v>513</v>
       </c>
       <c r="C488" t="s">
         <v>12</v>
@@ -17225,7 +17585,7 @@
         <v>488</v>
       </c>
       <c r="B489" t="s">
-        <v>389</v>
+        <v>514</v>
       </c>
       <c r="C489" t="s">
         <v>12</v>
@@ -17257,7 +17617,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="s">
-        <v>390</v>
+        <v>62</v>
       </c>
       <c r="C490" t="s">
         <v>12</v>
@@ -17289,7 +17649,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="s">
-        <v>391</v>
+        <v>63</v>
       </c>
       <c r="C491" t="s">
         <v>12</v>
@@ -17321,7 +17681,7 @@
         <v>491</v>
       </c>
       <c r="B492" t="s">
-        <v>392</v>
+        <v>515</v>
       </c>
       <c r="C492" t="s">
         <v>17</v>
@@ -17353,7 +17713,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="s">
-        <v>392</v>
+        <v>516</v>
       </c>
       <c r="C493" t="s">
         <v>17</v>
@@ -17385,7 +17745,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="s">
-        <v>393</v>
+        <v>64</v>
       </c>
       <c r="C494" t="s">
         <v>17</v>
@@ -17417,7 +17777,7 @@
         <v>494</v>
       </c>
       <c r="B495" t="s">
-        <v>394</v>
+        <v>65</v>
       </c>
       <c r="C495" t="s">
         <v>17</v>
@@ -17449,7 +17809,7 @@
         <v>495</v>
       </c>
       <c r="B496" t="s">
-        <v>395</v>
+        <v>66</v>
       </c>
       <c r="C496" t="s">
         <v>12</v>
